--- a/miniGAM/Dados/lançamentos_não_encontrados_no_excel.xlsx
+++ b/miniGAM/Dados/lançamentos_não_encontrados_no_excel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="738">
   <si>
     <t>Título Lido na Tela</t>
   </si>
@@ -25,13 +25,13 @@
     <t>Observação</t>
   </si>
   <si>
-    <t>9-700/1</t>
+    <t>9-70071</t>
   </si>
   <si>
     <t>15-700/1</t>
   </si>
   <si>
-    <t>25-7001</t>
+    <t>25-700/1</t>
   </si>
   <si>
     <t>30-700/1</t>
@@ -40,7 +40,7 @@
     <t>35-700/1</t>
   </si>
   <si>
-    <t>55-700/1</t>
+    <t>55-7001</t>
   </si>
   <si>
     <t>78-700/1</t>
@@ -52,739 +52,1267 @@
     <t>24-700/1</t>
   </si>
   <si>
+    <t>54-7001</t>
+  </si>
+  <si>
+    <t>75-700/1</t>
+  </si>
+  <si>
+    <t>51-7001</t>
+  </si>
+  <si>
+    <t>71-70011</t>
+  </si>
+  <si>
+    <t>123-7001</t>
+  </si>
+  <si>
+    <t>101-700/1</t>
+  </si>
+  <si>
+    <t>102-700/1</t>
+  </si>
+  <si>
+    <t>103-700/1</t>
+  </si>
+  <si>
+    <t>105-700/1</t>
+  </si>
+  <si>
+    <t>106-700/1</t>
+  </si>
+  <si>
+    <t>137-700/1</t>
+  </si>
+  <si>
+    <t>188-70071</t>
+  </si>
+  <si>
+    <t>73-700/1</t>
+  </si>
+  <si>
+    <t>14770071</t>
+  </si>
+  <si>
+    <t>130-700/1</t>
+  </si>
+  <si>
+    <t>133-700/1</t>
+  </si>
+  <si>
+    <t>134-700/1</t>
+  </si>
+  <si>
+    <t>150700/1</t>
+  </si>
+  <si>
+    <t>141-700/1</t>
+  </si>
+  <si>
+    <t>166-700/1</t>
+  </si>
+  <si>
+    <t>107700/1</t>
+  </si>
+  <si>
+    <t>170-700/1</t>
+  </si>
+  <si>
+    <t>181-700/1</t>
+  </si>
+  <si>
+    <t>182-700/1</t>
+  </si>
+  <si>
+    <t>183-70071</t>
+  </si>
+  <si>
+    <t>18770071</t>
+  </si>
+  <si>
+    <t>205-700/1</t>
+  </si>
+  <si>
+    <t>211-700/1</t>
+  </si>
+  <si>
+    <t>143-700/1</t>
+  </si>
+  <si>
+    <t>155-7001</t>
+  </si>
+  <si>
+    <t>327700/1</t>
+  </si>
+  <si>
+    <t>161-700/1</t>
+  </si>
+  <si>
+    <t>168-700/1</t>
+  </si>
+  <si>
+    <t>384-700/1</t>
+  </si>
+  <si>
+    <t>238-700/1</t>
+  </si>
+  <si>
+    <t>456-700/1</t>
+  </si>
+  <si>
+    <t>269-700/1</t>
+  </si>
+  <si>
+    <t>277700/1</t>
+  </si>
+  <si>
+    <t>278-700/1</t>
+  </si>
+  <si>
+    <t>279-700/1</t>
+  </si>
+  <si>
+    <t>145-700/1</t>
+  </si>
+  <si>
+    <t>209-700/1</t>
+  </si>
+  <si>
+    <t>492700/1</t>
+  </si>
+  <si>
+    <t>495-70071</t>
+  </si>
+  <si>
+    <t>29770071</t>
+  </si>
+  <si>
+    <t>344-7001</t>
+  </si>
+  <si>
+    <t>309-700/1</t>
+  </si>
+  <si>
+    <t>328-700/1</t>
+  </si>
+  <si>
+    <t>565-700/1</t>
+  </si>
+  <si>
+    <t>566-700/1</t>
+  </si>
+  <si>
+    <t>236-700/1</t>
+  </si>
+  <si>
+    <t>239-700/1</t>
+  </si>
+  <si>
+    <t>262-700/1</t>
+  </si>
+  <si>
+    <t>336-700/1</t>
+  </si>
+  <si>
+    <t>337-700/1</t>
+  </si>
+  <si>
+    <t>374-700/1</t>
+  </si>
+  <si>
+    <t>753-700/1</t>
+  </si>
+  <si>
+    <t>273-700/1</t>
+  </si>
+  <si>
+    <t>274-700/1</t>
+  </si>
+  <si>
+    <t>401-70071</t>
+  </si>
+  <si>
+    <t>333-700/1</t>
+  </si>
+  <si>
+    <t>397-700/1</t>
+  </si>
+  <si>
+    <t>710-70071</t>
+  </si>
+  <si>
+    <t>243-700/1</t>
+  </si>
+  <si>
+    <t>245-7001</t>
+  </si>
+  <si>
+    <t>246-700/1</t>
+  </si>
+  <si>
+    <t>247-700/1</t>
+  </si>
+  <si>
+    <t>440-70071</t>
+  </si>
+  <si>
+    <t>893-700/1</t>
+  </si>
+  <si>
+    <t>266-700/1</t>
+  </si>
+  <si>
+    <t>267-700/1</t>
+  </si>
+  <si>
+    <t>453-70071</t>
+  </si>
+  <si>
+    <t>303-700/1</t>
+  </si>
+  <si>
+    <t>379-700/1</t>
+  </si>
+  <si>
+    <t>381-700/1</t>
+  </si>
+  <si>
+    <t>780-700/1</t>
+  </si>
+  <si>
+    <t>329-700/1</t>
+  </si>
+  <si>
+    <t>417700/1</t>
+  </si>
+  <si>
+    <t>418-700/1</t>
+  </si>
+  <si>
+    <t>405-70071</t>
+  </si>
+  <si>
+    <t>429-700/1</t>
+  </si>
+  <si>
+    <t>332-700/1</t>
+  </si>
+  <si>
+    <t>366-700/1</t>
+  </si>
+  <si>
+    <t>368-700/1</t>
+  </si>
+  <si>
+    <t>496700/1</t>
+  </si>
+  <si>
+    <t>400-70071</t>
+  </si>
+  <si>
+    <t>402-70071</t>
+  </si>
+  <si>
+    <t>454-70071</t>
+  </si>
+  <si>
+    <t>470-70071</t>
+  </si>
+  <si>
+    <t>423-700/1</t>
+  </si>
+  <si>
+    <t>331-700/1</t>
+  </si>
+  <si>
+    <t>403-70071</t>
+  </si>
+  <si>
+    <t>517-700/1</t>
+  </si>
+  <si>
+    <t>393-700/1</t>
+  </si>
+  <si>
+    <t>439-700/1</t>
+  </si>
+  <si>
+    <t>485-700/1</t>
+  </si>
+  <si>
+    <t>539-700/1</t>
+  </si>
+  <si>
+    <t>603-700/1</t>
+  </si>
+  <si>
+    <t>1375-700/1</t>
+  </si>
+  <si>
+    <t>250700/1</t>
+  </si>
+  <si>
+    <t>252700/1</t>
+  </si>
+  <si>
+    <t>253700/1</t>
+  </si>
+  <si>
+    <t>255-7001</t>
+  </si>
+  <si>
+    <t>256-700/1</t>
+  </si>
+  <si>
+    <t>257700/1</t>
+  </si>
+  <si>
+    <t>419-700/1</t>
+  </si>
+  <si>
+    <t>479-70071</t>
+  </si>
+  <si>
+    <t>482-700/1</t>
+  </si>
+  <si>
+    <t>483-700/1</t>
+  </si>
+  <si>
+    <t>532-700/1</t>
+  </si>
+  <si>
+    <t>542-700/1</t>
+  </si>
+  <si>
+    <t>558-700/1</t>
+  </si>
+  <si>
+    <t>998-70071</t>
+  </si>
+  <si>
+    <t>474-70071</t>
+  </si>
+  <si>
+    <t>449-70071</t>
+  </si>
+  <si>
+    <t>644-700/1</t>
+  </si>
+  <si>
+    <t>465-70071</t>
+  </si>
+  <si>
+    <t>467-700/1</t>
+  </si>
+  <si>
+    <t>526-700/1</t>
+  </si>
+  <si>
+    <t>606-700/1</t>
+  </si>
+  <si>
+    <t>652-700/1</t>
+  </si>
+  <si>
+    <t>1045-700/1</t>
+  </si>
+  <si>
+    <t>444-70071</t>
+  </si>
+  <si>
+    <t>568-700/1</t>
+  </si>
+  <si>
+    <t>580-700/1</t>
+  </si>
+  <si>
+    <t>620-700/1</t>
+  </si>
+  <si>
+    <t>685-700/1</t>
+  </si>
+  <si>
+    <t>382-700/1</t>
+  </si>
+  <si>
+    <t>383-700/1</t>
+  </si>
+  <si>
+    <t>544-700/1</t>
+  </si>
+  <si>
+    <t>549-700/1</t>
+  </si>
+  <si>
+    <t>575-700/1</t>
+  </si>
+  <si>
+    <t>576-700/1</t>
+  </si>
+  <si>
+    <t>589-700/1</t>
+  </si>
+  <si>
+    <t>705-70071</t>
+  </si>
+  <si>
+    <t>1556-700/1</t>
+  </si>
+  <si>
+    <t>1557-700/1</t>
+  </si>
+  <si>
+    <t>1558-700/1</t>
+  </si>
+  <si>
+    <t>1582-700/1</t>
+  </si>
+  <si>
+    <t>548-700/1</t>
+  </si>
+  <si>
+    <t>683-700/1</t>
+  </si>
+  <si>
+    <t>634-700/1</t>
+  </si>
+  <si>
+    <t>1168-700/1</t>
+  </si>
+  <si>
+    <t>714-70071</t>
+  </si>
+  <si>
+    <t>557-700/1</t>
+  </si>
+  <si>
+    <t>596-700/1</t>
+  </si>
+  <si>
+    <t>687-700/1</t>
+  </si>
+  <si>
+    <t>764-70071</t>
+  </si>
+  <si>
+    <t>44770071</t>
+  </si>
+  <si>
+    <t>448-70071</t>
+  </si>
+  <si>
+    <t>640-700/1</t>
+  </si>
+  <si>
+    <t>643-700/1</t>
+  </si>
+  <si>
+    <t>1857700/1</t>
+  </si>
+  <si>
+    <t>484-70071</t>
+  </si>
+  <si>
+    <t>488-70071</t>
+  </si>
+  <si>
+    <t>711-70071</t>
+  </si>
+  <si>
+    <t>729-70071</t>
+  </si>
+  <si>
+    <t>684-70071</t>
+  </si>
+  <si>
+    <t>814-7001</t>
+  </si>
+  <si>
+    <t>718700/1</t>
+  </si>
+  <si>
+    <t>776-70071</t>
+  </si>
+  <si>
+    <t>77770011</t>
+  </si>
+  <si>
+    <t>779-70071</t>
+  </si>
+  <si>
+    <t>740700/1</t>
+  </si>
+  <si>
+    <t>355-7001</t>
+  </si>
+  <si>
+    <t>356-700/1</t>
+  </si>
+  <si>
+    <t>642-700/1</t>
+  </si>
+  <si>
+    <t>654-700/1</t>
+  </si>
+  <si>
+    <t>945-70071</t>
+  </si>
+  <si>
+    <t>791-70071</t>
+  </si>
+  <si>
+    <t>979-70071</t>
+  </si>
+  <si>
+    <t>2367700/1</t>
+  </si>
+  <si>
+    <t>886-70071</t>
+  </si>
+  <si>
+    <t>689-70071</t>
+  </si>
+  <si>
+    <t>1007-700/1</t>
+  </si>
+  <si>
+    <t>1057700/1</t>
+  </si>
+  <si>
+    <t>742700/1</t>
+  </si>
+  <si>
+    <t>743700/1</t>
+  </si>
+  <si>
+    <t>773-70071</t>
+  </si>
+  <si>
+    <t>820-7001</t>
+  </si>
+  <si>
+    <t>954-70071</t>
+  </si>
+  <si>
+    <t>959-70071</t>
+  </si>
+  <si>
+    <t>999-70071</t>
+  </si>
+  <si>
+    <t>2705700/1</t>
+  </si>
+  <si>
+    <t>386-700/1</t>
+  </si>
+  <si>
+    <t>1114-7001</t>
+  </si>
+  <si>
+    <t>848-700/1</t>
+  </si>
+  <si>
+    <t>850-7001</t>
+  </si>
+  <si>
+    <t>1170-7001</t>
+  </si>
+  <si>
+    <t>1845700/1</t>
+  </si>
+  <si>
+    <t>772-70071</t>
+  </si>
+  <si>
+    <t>1037700/1</t>
+  </si>
+  <si>
+    <t>187770071</t>
+  </si>
+  <si>
+    <t>934-700/1</t>
+  </si>
+  <si>
+    <t>1040700/1</t>
+  </si>
+  <si>
+    <t>5063-700/1</t>
+  </si>
+  <si>
+    <t>917700/1</t>
+  </si>
+  <si>
+    <t>1152-7001</t>
+  </si>
+  <si>
+    <t>1073700/1</t>
+  </si>
+  <si>
+    <t>1211-7001</t>
+  </si>
+  <si>
+    <t>1214-7001</t>
+  </si>
+  <si>
+    <t>1307700/1</t>
+  </si>
+  <si>
+    <t>1126-7001</t>
+  </si>
+  <si>
+    <t>2004-7001</t>
+  </si>
+  <si>
+    <t>1354-700/1</t>
+  </si>
+  <si>
+    <t>1019-700/1</t>
+  </si>
+  <si>
+    <t>3227-700/1</t>
+  </si>
+  <si>
+    <t>1117-7001</t>
+  </si>
+  <si>
+    <t>1228-700/1</t>
+  </si>
+  <si>
+    <t>872-700/1</t>
+  </si>
+  <si>
+    <t>1191-700/1</t>
+  </si>
+  <si>
+    <t>1330-700/1</t>
+  </si>
+  <si>
+    <t>1340-700/1</t>
+  </si>
+  <si>
+    <t>1413-700/1</t>
+  </si>
+  <si>
+    <t>2095-700/1</t>
+  </si>
+  <si>
+    <t>1127-7001</t>
+  </si>
+  <si>
+    <t>1411-700/1</t>
+  </si>
+  <si>
+    <t>3320-7001</t>
+  </si>
+  <si>
+    <t>1259-700/1</t>
+  </si>
+  <si>
+    <t>1389-700/1</t>
+  </si>
+  <si>
+    <t>1418-7001</t>
+  </si>
+  <si>
+    <t>907-700/1</t>
+  </si>
+  <si>
+    <t>1096-700/1</t>
+  </si>
+  <si>
+    <t>1306-700/1</t>
+  </si>
+  <si>
+    <t>1480-7001</t>
+  </si>
+  <si>
+    <t>1244-7001</t>
+  </si>
+  <si>
+    <t>1421-700/1</t>
+  </si>
+  <si>
+    <t>1434-700/1</t>
+  </si>
+  <si>
+    <t>2211-7001</t>
+  </si>
+  <si>
+    <t>463-700/1</t>
+  </si>
+  <si>
+    <t>464-70071</t>
+  </si>
+  <si>
+    <t>1261-700/1</t>
+  </si>
+  <si>
+    <t>1341-700/1</t>
+  </si>
+  <si>
+    <t>1342-700/1</t>
+  </si>
+  <si>
+    <t>1430-700/1</t>
+  </si>
+  <si>
+    <t>1471-7001</t>
+  </si>
+  <si>
+    <t>1133-700/1</t>
+  </si>
+  <si>
+    <t>1472700/1</t>
+  </si>
+  <si>
+    <t>1471-70071</t>
+  </si>
+  <si>
+    <t>1430-7001</t>
+  </si>
+  <si>
+    <t>1244-700/1</t>
+  </si>
+  <si>
+    <t>9077001</t>
+  </si>
+  <si>
+    <t>1389-7001</t>
+  </si>
+  <si>
+    <t>2095-7001</t>
+  </si>
+  <si>
+    <t>1413-7001</t>
+  </si>
+  <si>
+    <t>1340-7001</t>
+  </si>
+  <si>
+    <t>1191-7001</t>
+  </si>
+  <si>
+    <t>8727001</t>
+  </si>
+  <si>
+    <t>1380-7001</t>
+  </si>
+  <si>
+    <t>11177001</t>
+  </si>
+  <si>
+    <t>32277001</t>
+  </si>
+  <si>
+    <t>831-7001</t>
+  </si>
+  <si>
+    <t>1100-7001</t>
+  </si>
+  <si>
+    <t>811-7001</t>
+  </si>
+  <si>
+    <t>1920-7001</t>
+  </si>
+  <si>
+    <t>1148-7001</t>
+  </si>
+  <si>
+    <t>1040-700/1</t>
+  </si>
+  <si>
+    <t>934-7001</t>
+  </si>
+  <si>
+    <t>785-70071</t>
+  </si>
+  <si>
+    <t>2911-7001</t>
+  </si>
+  <si>
+    <t>1877700/1</t>
+  </si>
+  <si>
+    <t>1108-7001</t>
+  </si>
+  <si>
+    <t>891-7001</t>
+  </si>
+  <si>
+    <t>1020-7001</t>
+  </si>
+  <si>
+    <t>848-7001</t>
+  </si>
+  <si>
+    <t>1145-7001</t>
+  </si>
+  <si>
+    <t>386-7001</t>
+  </si>
+  <si>
+    <t>385-70071</t>
+  </si>
+  <si>
+    <t>384-7001</t>
+  </si>
+  <si>
+    <t>871-7001</t>
+  </si>
+  <si>
+    <t>823-7001</t>
+  </si>
+  <si>
+    <t>2705-7001</t>
+  </si>
+  <si>
+    <t>999-7001</t>
+  </si>
+  <si>
+    <t>1740-7001</t>
+  </si>
+  <si>
+    <t>1115-7001</t>
+  </si>
+  <si>
+    <t>1068-7001</t>
+  </si>
+  <si>
+    <t>973-7001</t>
+  </si>
+  <si>
+    <t>972-7001</t>
+  </si>
+  <si>
+    <t>971-7001</t>
+  </si>
+  <si>
+    <t>959-7001</t>
+  </si>
+  <si>
+    <t>954-7001</t>
+  </si>
+  <si>
+    <t>928-7001</t>
+  </si>
+  <si>
+    <t>786-70071</t>
+  </si>
+  <si>
+    <t>892-7001</t>
+  </si>
+  <si>
+    <t>773-700/1</t>
+  </si>
+  <si>
+    <t>742-700/1</t>
+  </si>
+  <si>
+    <t>2528-7001</t>
+  </si>
+  <si>
+    <t>993-7001</t>
+  </si>
+  <si>
+    <t>901-7001</t>
+  </si>
+  <si>
+    <t>985-7001</t>
+  </si>
+  <si>
+    <t>1007700/1</t>
+  </si>
+  <si>
+    <t>689-7001</t>
+  </si>
+  <si>
+    <t>688-7001</t>
+  </si>
+  <si>
+    <t>1580-7001</t>
+  </si>
+  <si>
+    <t>886-7001</t>
+  </si>
+  <si>
+    <t>2367-7001</t>
+  </si>
+  <si>
+    <t>2362-7001</t>
+  </si>
+  <si>
+    <t>1567700/1</t>
+  </si>
+  <si>
+    <t>979-7001</t>
+  </si>
+  <si>
+    <t>3577001</t>
+  </si>
+  <si>
+    <t>945-7001</t>
+  </si>
+  <si>
+    <t>942-7001</t>
+  </si>
+  <si>
+    <t>836-7001</t>
+  </si>
+  <si>
+    <t>835-7001</t>
+  </si>
+  <si>
+    <t>642-7001</t>
+  </si>
+  <si>
+    <t>356-7001</t>
+  </si>
+  <si>
+    <t>740-7001</t>
+  </si>
+  <si>
+    <t>730-7001</t>
+  </si>
+  <si>
+    <t>869-7001</t>
+  </si>
+  <si>
+    <t>779-7001</t>
+  </si>
+  <si>
+    <t>573-7001</t>
+  </si>
+  <si>
+    <t>905-7001</t>
+  </si>
+  <si>
+    <t>846-7001</t>
+  </si>
+  <si>
+    <t>2058-7001</t>
+  </si>
+  <si>
+    <t>866-7001</t>
+  </si>
+  <si>
+    <t>729-7001</t>
+  </si>
+  <si>
+    <t>669-7001</t>
+  </si>
+  <si>
+    <t>668-7001</t>
+  </si>
+  <si>
+    <t>512-7001</t>
+  </si>
+  <si>
+    <t>485-70071</t>
+  </si>
+  <si>
+    <t>822-7001</t>
+  </si>
+  <si>
+    <t>806-7001</t>
+  </si>
+  <si>
+    <t>682-7001</t>
+  </si>
+  <si>
+    <t>643-7001</t>
+  </si>
+  <si>
+    <t>640-7001</t>
+  </si>
+  <si>
+    <t>496-70071</t>
+  </si>
+  <si>
+    <t>447700/1</t>
+  </si>
+  <si>
+    <t>687700/1</t>
+  </si>
+  <si>
+    <t>596-7001</t>
+  </si>
+  <si>
+    <t>5577001</t>
+  </si>
+  <si>
+    <t>714-700/1</t>
+  </si>
+  <si>
+    <t>1168-7001</t>
+  </si>
+  <si>
+    <t>683-7001</t>
+  </si>
+  <si>
+    <t>568-7001</t>
+  </si>
+  <si>
+    <t>548-7001</t>
+  </si>
+  <si>
+    <t>1582-7001</t>
+  </si>
+  <si>
+    <t>1558-7001</t>
+  </si>
+  <si>
+    <t>15577001</t>
+  </si>
+  <si>
+    <t>705-7001</t>
+  </si>
+  <si>
+    <t>589-7001</t>
+  </si>
+  <si>
+    <t>575-7001</t>
+  </si>
+  <si>
+    <t>549-7001</t>
+  </si>
+  <si>
+    <t>544-70071</t>
+  </si>
+  <si>
+    <t>383-70071</t>
+  </si>
+  <si>
+    <t>382-7001</t>
+  </si>
+  <si>
+    <t>381-7001</t>
+  </si>
+  <si>
+    <t>685-7001</t>
+  </si>
+  <si>
+    <t>620-7001</t>
+  </si>
+  <si>
+    <t>580-7001</t>
+  </si>
+  <si>
+    <t>652-7001</t>
+  </si>
+  <si>
+    <t>606-7001</t>
+  </si>
+  <si>
+    <t>529-7001</t>
+  </si>
+  <si>
+    <t>528-7001</t>
+  </si>
+  <si>
+    <t>527700/1</t>
+  </si>
+  <si>
+    <t>467-70071</t>
+  </si>
+  <si>
+    <t>998-7001</t>
+  </si>
+  <si>
+    <t>558-7001</t>
+  </si>
+  <si>
+    <t>542-7001</t>
+  </si>
+  <si>
+    <t>532-7001</t>
+  </si>
+  <si>
+    <t>483-70071</t>
+  </si>
+  <si>
+    <t>482-70071</t>
+  </si>
+  <si>
+    <t>419-70071</t>
+  </si>
+  <si>
+    <t>254-7001</t>
+  </si>
+  <si>
+    <t>253-7001</t>
+  </si>
+  <si>
+    <t>252-7001</t>
+  </si>
+  <si>
+    <t>251-7001</t>
+  </si>
+  <si>
+    <t>250-7001</t>
+  </si>
+  <si>
+    <t>603-7001</t>
+  </si>
+  <si>
+    <t>539-7001</t>
+  </si>
+  <si>
+    <t>439-70071</t>
+  </si>
+  <si>
+    <t>393-7001</t>
+  </si>
+  <si>
+    <t>331-7001</t>
+  </si>
+  <si>
+    <t>402-700/1</t>
+  </si>
+  <si>
+    <t>368-7001</t>
+  </si>
+  <si>
+    <t>418-70071</t>
+  </si>
+  <si>
+    <t>417-700/1</t>
+  </si>
+  <si>
+    <t>329-7001</t>
+  </si>
+  <si>
+    <t>780-7001</t>
+  </si>
+  <si>
+    <t>379-7001</t>
+  </si>
+  <si>
+    <t>303-7001</t>
+  </si>
+  <si>
+    <t>456-70071</t>
+  </si>
+  <si>
+    <t>267700/1</t>
+  </si>
+  <si>
+    <t>893-7001</t>
+  </si>
+  <si>
+    <t>247700/1</t>
+  </si>
+  <si>
+    <t>245-700/1</t>
+  </si>
+  <si>
+    <t>710-700/1</t>
+  </si>
+  <si>
+    <t>397700/1</t>
+  </si>
+  <si>
+    <t>279-7001</t>
+  </si>
+  <si>
+    <t>753-70071</t>
+  </si>
+  <si>
+    <t>337700/1</t>
+  </si>
+  <si>
+    <t>239-7001</t>
+  </si>
+  <si>
+    <t>565-7001</t>
+  </si>
+  <si>
+    <t>328-7001</t>
+  </si>
+  <si>
+    <t>309-7001</t>
+  </si>
+  <si>
+    <t>344-700/1</t>
+  </si>
+  <si>
+    <t>297700/1</t>
+  </si>
+  <si>
+    <t>278-7001</t>
+  </si>
+  <si>
+    <t>492-70071</t>
+  </si>
+  <si>
+    <t>209-7001</t>
+  </si>
+  <si>
+    <t>145-7001</t>
+  </si>
+  <si>
+    <t>269-7001</t>
+  </si>
+  <si>
+    <t>238-7001</t>
+  </si>
+  <si>
+    <t>155-700/1</t>
+  </si>
+  <si>
+    <t>211-7001</t>
+  </si>
+  <si>
+    <t>205-7001</t>
+  </si>
+  <si>
+    <t>123-700/1</t>
+  </si>
+  <si>
+    <t>187-70071</t>
+  </si>
+  <si>
+    <t>183-700/1</t>
+  </si>
+  <si>
+    <t>181-70071</t>
+  </si>
+  <si>
+    <t>170-7001</t>
+  </si>
+  <si>
+    <t>107-700/1</t>
+  </si>
+  <si>
+    <t>141-7001</t>
+  </si>
+  <si>
+    <t>150-7001</t>
+  </si>
+  <si>
+    <t>130-7001</t>
+  </si>
+  <si>
+    <t>147700/1</t>
+  </si>
+  <si>
+    <t>188-7001</t>
+  </si>
+  <si>
+    <t>71-7001</t>
+  </si>
+  <si>
+    <t>75-70071</t>
+  </si>
+  <si>
     <t>54-700/1</t>
   </si>
   <si>
-    <t>75-700/1</t>
-  </si>
-  <si>
-    <t>51-700/1</t>
-  </si>
-  <si>
-    <t>71-700/1</t>
-  </si>
-  <si>
-    <t>123-700/1</t>
-  </si>
-  <si>
-    <t>101-700/1</t>
-  </si>
-  <si>
-    <t>102-700/1</t>
-  </si>
-  <si>
-    <t>103-700/1</t>
-  </si>
-  <si>
-    <t>105-700/1</t>
-  </si>
-  <si>
-    <t>106-700/1</t>
-  </si>
-  <si>
-    <t>137700/1</t>
-  </si>
-  <si>
-    <t>18870071</t>
-  </si>
-  <si>
-    <t>73-700/1</t>
-  </si>
-  <si>
-    <t>147700/1</t>
-  </si>
-  <si>
-    <t>130-700/1</t>
-  </si>
-  <si>
-    <t>133-700/1</t>
-  </si>
-  <si>
-    <t>134-700/1</t>
-  </si>
-  <si>
-    <t>150-700/1</t>
-  </si>
-  <si>
-    <t>141-700/1</t>
-  </si>
-  <si>
-    <t>166-700/1</t>
-  </si>
-  <si>
-    <t>107700/1</t>
-  </si>
-  <si>
-    <t>170-700/1</t>
-  </si>
-  <si>
-    <t>181-700/1</t>
-  </si>
-  <si>
-    <t>182-700/1</t>
-  </si>
-  <si>
-    <t>183-700/1</t>
-  </si>
-  <si>
-    <t>187700/1</t>
-  </si>
-  <si>
-    <t>205-700/1</t>
-  </si>
-  <si>
-    <t>211-700/1</t>
-  </si>
-  <si>
-    <t>143-700/1</t>
-  </si>
-  <si>
-    <t>155-700/1</t>
-  </si>
-  <si>
-    <t>327700/1</t>
-  </si>
-  <si>
-    <t>161-700/1</t>
-  </si>
-  <si>
-    <t>168-700/1</t>
-  </si>
-  <si>
-    <t>384-700/1</t>
-  </si>
-  <si>
-    <t>238-700/1</t>
-  </si>
-  <si>
-    <t>456-700/1</t>
-  </si>
-  <si>
-    <t>269-700/1</t>
-  </si>
-  <si>
-    <t>277700/1</t>
-  </si>
-  <si>
-    <t>278700/1</t>
-  </si>
-  <si>
-    <t>279700/1</t>
-  </si>
-  <si>
-    <t>145-700/1</t>
-  </si>
-  <si>
-    <t>209-700/1</t>
-  </si>
-  <si>
-    <t>492700/1</t>
-  </si>
-  <si>
-    <t>495-70071</t>
-  </si>
-  <si>
-    <t>297700/1</t>
-  </si>
-  <si>
-    <t>344-700/1</t>
-  </si>
-  <si>
-    <t>309-700/1</t>
-  </si>
-  <si>
-    <t>328-700/1</t>
-  </si>
-  <si>
-    <t>565-700/1</t>
-  </si>
-  <si>
-    <t>566-700/1</t>
-  </si>
-  <si>
-    <t>236-700/1</t>
-  </si>
-  <si>
-    <t>239-700/1</t>
-  </si>
-  <si>
-    <t>262-700/1</t>
-  </si>
-  <si>
-    <t>336-700/1</t>
-  </si>
-  <si>
-    <t>337700/1</t>
-  </si>
-  <si>
-    <t>374-700/1</t>
-  </si>
-  <si>
-    <t>753-70071</t>
-  </si>
-  <si>
-    <t>273700/1</t>
-  </si>
-  <si>
-    <t>274-700/1</t>
-  </si>
-  <si>
-    <t>401-700/1</t>
-  </si>
-  <si>
-    <t>333-700/1</t>
-  </si>
-  <si>
-    <t>397700/1</t>
-  </si>
-  <si>
-    <t>710-700/1</t>
-  </si>
-  <si>
-    <t>243700/1</t>
-  </si>
-  <si>
-    <t>245-700/1</t>
-  </si>
-  <si>
-    <t>246-700/1</t>
-  </si>
-  <si>
-    <t>247700/1</t>
-  </si>
-  <si>
-    <t>440-700/1</t>
-  </si>
-  <si>
-    <t>893-70071</t>
-  </si>
-  <si>
-    <t>266-700/1</t>
-  </si>
-  <si>
-    <t>267700/1</t>
-  </si>
-  <si>
-    <t>453-700/1</t>
-  </si>
-  <si>
-    <t>303-700/1</t>
-  </si>
-  <si>
-    <t>379700/1</t>
-  </si>
-  <si>
-    <t>381-700/1</t>
-  </si>
-  <si>
-    <t>780-70071</t>
-  </si>
-  <si>
-    <t>329-700/1</t>
-  </si>
-  <si>
-    <t>417700/1</t>
-  </si>
-  <si>
-    <t>418700/1</t>
-  </si>
-  <si>
-    <t>405-700/1</t>
-  </si>
-  <si>
-    <t>429-700/1</t>
-  </si>
-  <si>
-    <t>332-700/1</t>
-  </si>
-  <si>
-    <t>366-700/1</t>
-  </si>
-  <si>
-    <t>368-70071</t>
-  </si>
-  <si>
-    <t>496-70071</t>
-  </si>
-  <si>
-    <t>400700/1</t>
-  </si>
-  <si>
-    <t>402700/1</t>
-  </si>
-  <si>
-    <t>454-70071</t>
-  </si>
-  <si>
-    <t>470700/1</t>
-  </si>
-  <si>
-    <t>423-700/1</t>
-  </si>
-  <si>
-    <t>331-700/1</t>
-  </si>
-  <si>
-    <t>403700/1</t>
-  </si>
-  <si>
-    <t>517700/1</t>
-  </si>
-  <si>
-    <t>393-700/1</t>
-  </si>
-  <si>
-    <t>439-700/1</t>
-  </si>
-  <si>
-    <t>485-70071</t>
-  </si>
-  <si>
-    <t>539-700/1</t>
-  </si>
-  <si>
-    <t>603-700/1</t>
-  </si>
-  <si>
-    <t>1375-700/1</t>
-  </si>
-  <si>
-    <t>255-700/1</t>
-  </si>
-  <si>
-    <t>256-700/1</t>
-  </si>
-  <si>
-    <t>257700/1</t>
-  </si>
-  <si>
-    <t>419700/1</t>
-  </si>
-  <si>
-    <t>47970071</t>
-  </si>
-  <si>
-    <t>482700/1</t>
-  </si>
-  <si>
-    <t>48370071</t>
-  </si>
-  <si>
-    <t>532700/1</t>
-  </si>
-  <si>
-    <t>542-700/1</t>
-  </si>
-  <si>
-    <t>558-700/1</t>
-  </si>
-  <si>
-    <t>998700/1</t>
-  </si>
-  <si>
-    <t>474-700/1</t>
-  </si>
-  <si>
-    <t>44970071</t>
-  </si>
-  <si>
-    <t>644-700/1</t>
-  </si>
-  <si>
-    <t>465700/1</t>
-  </si>
-  <si>
-    <t>467700/1</t>
-  </si>
-  <si>
-    <t>526-700/1</t>
-  </si>
-  <si>
-    <t>528700/1</t>
-  </si>
-  <si>
-    <t>606-700/1</t>
-  </si>
-  <si>
-    <t>652-700/1</t>
-  </si>
-  <si>
-    <t>1045-700/1</t>
-  </si>
-  <si>
-    <t>444-700/1</t>
-  </si>
-  <si>
-    <t>568700/1</t>
-  </si>
-  <si>
-    <t>580700/1</t>
-  </si>
-  <si>
-    <t>620-700/1</t>
-  </si>
-  <si>
-    <t>685-70071</t>
-  </si>
-  <si>
-    <t>382-700/1</t>
-  </si>
-  <si>
-    <t>383-700/1</t>
-  </si>
-  <si>
-    <t>544-700/1</t>
-  </si>
-  <si>
-    <t>549-700/1</t>
-  </si>
-  <si>
-    <t>575-700/1</t>
-  </si>
-  <si>
-    <t>576-700/1</t>
-  </si>
-  <si>
-    <t>589700/1</t>
-  </si>
-  <si>
-    <t>705-70071</t>
-  </si>
-  <si>
-    <t>1556-700/1</t>
-  </si>
-  <si>
-    <t>1557700/1</t>
-  </si>
-  <si>
-    <t>1558-700/1</t>
-  </si>
-  <si>
-    <t>1582-700/1</t>
-  </si>
-  <si>
-    <t>548-700/1</t>
-  </si>
-  <si>
-    <t>683700/1</t>
-  </si>
-  <si>
-    <t>634-700/1</t>
-  </si>
-  <si>
-    <t>1168-700/1</t>
-  </si>
-  <si>
-    <t>714-700/1</t>
-  </si>
-  <si>
-    <t>557700/1</t>
-  </si>
-  <si>
-    <t>596-700/1</t>
-  </si>
-  <si>
-    <t>447700/1</t>
-  </si>
-  <si>
-    <t>448-700/1</t>
-  </si>
-  <si>
-    <t>640-700/1</t>
-  </si>
-  <si>
-    <t>643700/1</t>
-  </si>
-  <si>
-    <t>682700/1</t>
-  </si>
-  <si>
-    <t>1857700/1</t>
-  </si>
-  <si>
-    <t>806-70071</t>
-  </si>
-  <si>
-    <t>822700/1</t>
-  </si>
-  <si>
-    <t>484-70071</t>
-  </si>
-  <si>
-    <t>48870071</t>
-  </si>
-  <si>
-    <t>785-70071</t>
-  </si>
-  <si>
-    <t>512700/1</t>
-  </si>
-  <si>
-    <t>796-70071</t>
-  </si>
-  <si>
-    <t>866-70071</t>
-  </si>
-  <si>
-    <t>718700/1</t>
-  </si>
-  <si>
-    <t>846700/1</t>
-  </si>
-  <si>
-    <t>776-70071</t>
-  </si>
-  <si>
-    <t>77770071</t>
-  </si>
-  <si>
-    <t>779-70071</t>
-  </si>
-  <si>
-    <t>869-70071</t>
-  </si>
-  <si>
-    <t>355-700/1</t>
-  </si>
-  <si>
-    <t>356-700/1</t>
-  </si>
-  <si>
-    <t>642700/1</t>
-  </si>
-  <si>
-    <t>813700/1</t>
-  </si>
-  <si>
-    <t>654-700/1</t>
-  </si>
-  <si>
-    <t>835-70071</t>
-  </si>
-  <si>
-    <t>919700/1</t>
-  </si>
-  <si>
-    <t>942700/1</t>
-  </si>
-  <si>
-    <t>945700/1</t>
-  </si>
-  <si>
-    <t>357700/1</t>
-  </si>
-  <si>
-    <t>979700/1</t>
-  </si>
-  <si>
-    <t>1567700/1</t>
-  </si>
-  <si>
-    <t>2367700/1</t>
-  </si>
-  <si>
-    <t>632700/1</t>
-  </si>
-  <si>
-    <t>886-70071</t>
-  </si>
-  <si>
-    <t>688-70071</t>
-  </si>
-  <si>
-    <t>689-70071</t>
-  </si>
-  <si>
-    <t>1007700/1</t>
-  </si>
-  <si>
-    <t>913700/1</t>
-  </si>
-  <si>
-    <t>985700/1</t>
-  </si>
-  <si>
-    <t>993700/1</t>
-  </si>
-  <si>
-    <t>1057700/1</t>
-  </si>
-  <si>
-    <t>2528700/1</t>
-  </si>
-  <si>
-    <t>742700/1</t>
-  </si>
-  <si>
-    <t>773-70071</t>
-  </si>
-  <si>
-    <t>820700/1</t>
-  </si>
-  <si>
-    <t>892700/1</t>
-  </si>
-  <si>
-    <t>786-70071</t>
-  </si>
-  <si>
-    <t>928700/1</t>
-  </si>
-  <si>
-    <t>972700/1</t>
-  </si>
-  <si>
-    <t>973700/1</t>
-  </si>
-  <si>
-    <t>1740700/1</t>
-  </si>
-  <si>
-    <t>999700/1</t>
-  </si>
-  <si>
-    <t>386-700/1</t>
-  </si>
-  <si>
-    <t>848700/1</t>
-  </si>
-  <si>
-    <t>850-70071</t>
-  </si>
-  <si>
-    <t>772700/1</t>
-  </si>
-  <si>
-    <t>891-70071</t>
-  </si>
-  <si>
-    <t>1037700/1</t>
-  </si>
-  <si>
-    <t>1877700/1</t>
-  </si>
-  <si>
-    <t>934-700/1</t>
-  </si>
-  <si>
-    <t>1040700/1</t>
-  </si>
-  <si>
-    <t>5063-700/1</t>
-  </si>
-  <si>
-    <t>917700/1</t>
-  </si>
-  <si>
-    <t>1232700/1</t>
-  </si>
-  <si>
-    <t>1307700/1</t>
-  </si>
-  <si>
-    <t>1354-700/1</t>
-  </si>
-  <si>
-    <t>1019-700/1</t>
-  </si>
-  <si>
-    <t>3227700/1</t>
-  </si>
-  <si>
-    <t>1117700/1</t>
-  </si>
-  <si>
-    <t>1228-700/1</t>
-  </si>
-  <si>
-    <t>872700/1</t>
-  </si>
-  <si>
-    <t>1191-700/1</t>
-  </si>
-  <si>
-    <t>1330-700/1</t>
-  </si>
-  <si>
-    <t>1340-700/1</t>
-  </si>
-  <si>
-    <t>1413-700/1</t>
-  </si>
-  <si>
-    <t>2095-700/1</t>
-  </si>
-  <si>
-    <t>1127700/1</t>
-  </si>
-  <si>
-    <t>1411-700/1</t>
-  </si>
-  <si>
-    <t>3320-700/1</t>
-  </si>
-  <si>
-    <t>1259-700/1</t>
-  </si>
-  <si>
-    <t>1389-700/1</t>
-  </si>
-  <si>
-    <t>1418-700/1</t>
-  </si>
-  <si>
-    <t>907700/1</t>
-  </si>
-  <si>
-    <t>1096-700/1</t>
-  </si>
-  <si>
-    <t>1306-700/1</t>
-  </si>
-  <si>
-    <t>1480-700/1</t>
-  </si>
-  <si>
-    <t>1244-700/1</t>
-  </si>
-  <si>
-    <t>1421-700/1</t>
-  </si>
-  <si>
-    <t>1434-700/1</t>
-  </si>
-  <si>
-    <t>2211-700/1</t>
-  </si>
-  <si>
-    <t>463700/1</t>
-  </si>
-  <si>
-    <t>464-700/1</t>
-  </si>
-  <si>
-    <t>1261-700/1</t>
-  </si>
-  <si>
-    <t>1341-700/1</t>
-  </si>
-  <si>
-    <t>1342-700/1</t>
-  </si>
-  <si>
-    <t>1430-700/1</t>
-  </si>
-  <si>
-    <t>1471-700/1</t>
-  </si>
-  <si>
-    <t>1133-700/1</t>
-  </si>
-  <si>
-    <t>1472-700/1</t>
-  </si>
-  <si>
-    <t>463-700/1</t>
+    <t>21-7001</t>
+  </si>
+  <si>
+    <t>78-7001</t>
   </si>
   <si>
     <t>37.44</t>
@@ -799,15 +1327,12 @@
     <t>69.12</t>
   </si>
   <si>
-    <t>5.99</t>
+    <t>665</t>
   </si>
   <si>
     <t>5.76</t>
   </si>
   <si>
-    <t>69,12</t>
-  </si>
-  <si>
     <t>25.92</t>
   </si>
   <si>
@@ -841,10 +1366,10 @@
     <t>25.63</t>
   </si>
   <si>
-    <t>67.87</t>
-  </si>
-  <si>
-    <t>397.98</t>
+    <t>10,01</t>
+  </si>
+  <si>
+    <t>.98</t>
   </si>
   <si>
     <t>276.98</t>
@@ -868,7 +1393,7 @@
     <t>6.05</t>
   </si>
   <si>
-    <t>140.00</t>
+    <t>140,00</t>
   </si>
   <si>
     <t>273.88</t>
@@ -880,7 +1405,7 @@
     <t>18.73</t>
   </si>
   <si>
-    <t>48.31</t>
+    <t>13.35</t>
   </si>
   <si>
     <t>7.39</t>
@@ -892,601 +1417,814 @@
     <t>12.06</t>
   </si>
   <si>
+    <t>72.00</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>512.30</t>
+  </si>
+  <si>
+    <t>166.07</t>
+  </si>
+  <si>
+    <t>115.08</t>
+  </si>
+  <si>
+    <t>144.04</t>
+  </si>
+  <si>
+    <t>48.75</t>
+  </si>
+  <si>
+    <t>384.28</t>
+  </si>
+  <si>
+    <t>53.17</t>
+  </si>
+  <si>
+    <t>11,41</t>
+  </si>
+  <si>
+    <t>248.16</t>
+  </si>
+  <si>
+    <t>175.53</t>
+  </si>
+  <si>
+    <t>516.48</t>
+  </si>
+  <si>
+    <t>242.37</t>
+  </si>
+  <si>
+    <t>757.97</t>
+  </si>
+  <si>
+    <t>19.25</t>
+  </si>
+  <si>
+    <t>5.63</t>
+  </si>
+  <si>
+    <t>399.77</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>19.90</t>
+  </si>
+  <si>
+    <t>11,00</t>
+  </si>
+  <si>
+    <t>447.21</t>
+  </si>
+  <si>
+    <t>11.52</t>
+  </si>
+  <si>
+    <t>19.77</t>
+  </si>
+  <si>
+    <t>21.19</t>
+  </si>
+  <si>
+    <t>78.24</t>
+  </si>
+  <si>
+    <t>215.43</t>
+  </si>
+  <si>
+    <t>80.47</t>
+  </si>
+  <si>
+    <t>50.79</t>
+  </si>
+  <si>
+    <t>109,25</t>
+  </si>
+  <si>
+    <t>78.30</t>
+  </si>
+  <si>
+    <t>8.64</t>
+  </si>
+  <si>
+    <t>207.76</t>
+  </si>
+  <si>
+    <t>384.64</t>
+  </si>
+  <si>
+    <t>130,13</t>
+  </si>
+  <si>
+    <t>7.92</t>
+  </si>
+  <si>
+    <t>45.24</t>
+  </si>
+  <si>
+    <t>122.90</t>
+  </si>
+  <si>
+    <t>300.08</t>
+  </si>
+  <si>
+    <t>76.98</t>
+  </si>
+  <si>
+    <t>8.51</t>
+  </si>
+  <si>
+    <t>86.68</t>
+  </si>
+  <si>
+    <t>251.28</t>
+  </si>
+  <si>
+    <t>127.72</t>
+  </si>
+  <si>
+    <t>19.29</t>
+  </si>
+  <si>
+    <t>61.80</t>
+  </si>
+  <si>
+    <t>472.08</t>
+  </si>
+  <si>
+    <t>252.88</t>
+  </si>
+  <si>
+    <t>121,.32</t>
+  </si>
+  <si>
+    <t>171.40</t>
+  </si>
+  <si>
+    <t>390,65</t>
+  </si>
+  <si>
+    <t>255,64</t>
+  </si>
+  <si>
+    <t>72.14</t>
+  </si>
+  <si>
+    <t>45.23</t>
+  </si>
+  <si>
+    <t>65,50</t>
+  </si>
+  <si>
+    <t>74.02</t>
+  </si>
+  <si>
+    <t>130.20</t>
+  </si>
+  <si>
+    <t>90.80</t>
+  </si>
+  <si>
+    <t>5,50</t>
+  </si>
+  <si>
+    <t>181.98</t>
+  </si>
+  <si>
+    <t>64.66</t>
+  </si>
+  <si>
+    <t>13,20</t>
+  </si>
+  <si>
+    <t>386.68</t>
+  </si>
+  <si>
+    <t>10.27</t>
+  </si>
+  <si>
+    <t>106.54</t>
+  </si>
+  <si>
+    <t>52.16</t>
+  </si>
+  <si>
+    <t>20.93</t>
+  </si>
+  <si>
+    <t>3.37</t>
+  </si>
+  <si>
+    <t>214.29</t>
+  </si>
+  <si>
+    <t>113.85</t>
+  </si>
+  <si>
+    <t>117.36</t>
+  </si>
+  <si>
+    <t>188.28</t>
+  </si>
+  <si>
+    <t>78.45</t>
+  </si>
+  <si>
+    <t>83.20</t>
+  </si>
+  <si>
+    <t>87.66</t>
+  </si>
+  <si>
+    <t>131.61</t>
+  </si>
+  <si>
+    <t>446.31</t>
+  </si>
+  <si>
+    <t>332.80</t>
+  </si>
+  <si>
+    <t>166.40</t>
+  </si>
+  <si>
+    <t>195.54</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>14.85</t>
+  </si>
+  <si>
+    <t>16.03</t>
+  </si>
+  <si>
+    <t>100.88</t>
+  </si>
+  <si>
+    <t>108.48</t>
+  </si>
+  <si>
+    <t>107.12</t>
+  </si>
+  <si>
+    <t>66.30</t>
+  </si>
+  <si>
+    <t>22,37</t>
+  </si>
+  <si>
+    <t>66.50</t>
+  </si>
+  <si>
+    <t>51.59</t>
+  </si>
+  <si>
+    <t>6.74</t>
+  </si>
+  <si>
+    <t>33.91</t>
+  </si>
+  <si>
+    <t>244.80</t>
+  </si>
+  <si>
+    <t>195.10</t>
+  </si>
+  <si>
+    <t>213.12</t>
+  </si>
+  <si>
+    <t>184.32</t>
+  </si>
+  <si>
+    <t>215.20</t>
+  </si>
+  <si>
+    <t>139.54</t>
+  </si>
+  <si>
+    <t>2.75</t>
+  </si>
+  <si>
+    <t>10.51</t>
+  </si>
+  <si>
+    <t>239.55</t>
+  </si>
+  <si>
+    <t>94.03</t>
+  </si>
+  <si>
+    <t>206.50</t>
+  </si>
+  <si>
+    <t>204.63</t>
+  </si>
+  <si>
+    <t>194.70</t>
+  </si>
+  <si>
+    <t>52.27</t>
+  </si>
+  <si>
+    <t>666</t>
+  </si>
+  <si>
+    <t>74.04</t>
+  </si>
+  <si>
+    <t>110.01</t>
+  </si>
+  <si>
+    <t>65.37</t>
+  </si>
+  <si>
+    <t>156.94</t>
+  </si>
+  <si>
+    <t>222.14</t>
+  </si>
+  <si>
+    <t>25.34</t>
+  </si>
+  <si>
+    <t>296.56</t>
+  </si>
+  <si>
+    <t>293.19</t>
+  </si>
+  <si>
+    <t>363.23</t>
+  </si>
+  <si>
+    <t>418.25</t>
+  </si>
+  <si>
+    <t>61.05</t>
+  </si>
+  <si>
+    <t>231,00</t>
+  </si>
+  <si>
+    <t>22,07</t>
+  </si>
+  <si>
+    <t>21.11</t>
+  </si>
+  <si>
+    <t>40.44</t>
+  </si>
+  <si>
+    <t>80.88</t>
+  </si>
+  <si>
+    <t>54.48</t>
+  </si>
+  <si>
+    <t>45.50</t>
+  </si>
+  <si>
+    <t>225.80</t>
+  </si>
+  <si>
+    <t>204.48</t>
+  </si>
+  <si>
+    <t>55.64</t>
+  </si>
+  <si>
+    <t>41.60</t>
+  </si>
+  <si>
+    <t>103,81</t>
+  </si>
+  <si>
+    <t>124.80</t>
+  </si>
+  <si>
+    <t>5.28</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>39.12</t>
+  </si>
+  <si>
+    <t>71.30</t>
+  </si>
+  <si>
+    <t>79.95</t>
+  </si>
+  <si>
+    <t>222.07</t>
+  </si>
+  <si>
+    <t>150.39</t>
+  </si>
+  <si>
+    <t>16.73</t>
+  </si>
+  <si>
+    <t>13.48</t>
+  </si>
+  <si>
+    <t>32.50</t>
+  </si>
+  <si>
+    <t>123.89</t>
+  </si>
+  <si>
+    <t>57.29</t>
+  </si>
+  <si>
+    <t>488.43</t>
+  </si>
+  <si>
+    <t>26.36</t>
+  </si>
+  <si>
+    <t>273.32</t>
+  </si>
+  <si>
+    <t>112.57</t>
+  </si>
+  <si>
+    <t>256.49</t>
+  </si>
+  <si>
+    <t>126.51</t>
+  </si>
+  <si>
+    <t>68.25</t>
+  </si>
+  <si>
+    <t>90.63</t>
+  </si>
+  <si>
+    <t>669.82</t>
+  </si>
+  <si>
+    <t>421.35</t>
+  </si>
+  <si>
+    <t>48.73</t>
+  </si>
+  <si>
+    <t>46.31</t>
+  </si>
+  <si>
+    <t>167.41</t>
+  </si>
+  <si>
+    <t>98.03</t>
+  </si>
+  <si>
+    <t>66.97</t>
+  </si>
+  <si>
+    <t>43.09</t>
+  </si>
+  <si>
+    <t>42.71</t>
+  </si>
+  <si>
+    <t>33.25</t>
+  </si>
+  <si>
+    <t>52,24</t>
+  </si>
+  <si>
+    <t>362.54</t>
+  </si>
+  <si>
+    <t>24.07</t>
+  </si>
+  <si>
+    <t>343.73</t>
+  </si>
+  <si>
+    <t>345.23</t>
+  </si>
+  <si>
+    <t>51.84</t>
+  </si>
+  <si>
+    <t>29,20</t>
+  </si>
+  <si>
+    <t>20.53</t>
+  </si>
+  <si>
+    <t>65.36</t>
+  </si>
+  <si>
+    <t>83.71</t>
+  </si>
+  <si>
+    <t>95.78</t>
+  </si>
+  <si>
+    <t>262.86</t>
+  </si>
+  <si>
+    <t>337.20</t>
+  </si>
+  <si>
+    <t>18.49</t>
+  </si>
+  <si>
+    <t>187.36</t>
+  </si>
+  <si>
+    <t>101.23</t>
+  </si>
+  <si>
+    <t>13.12</t>
+  </si>
+  <si>
+    <t>24,00</t>
+  </si>
+  <si>
+    <t>53.92</t>
+  </si>
+  <si>
+    <t>29.25</t>
+  </si>
+  <si>
+    <t>204.78</t>
+  </si>
+  <si>
+    <t>21.74</t>
+  </si>
+  <si>
+    <t>235,90</t>
+  </si>
+  <si>
+    <t>48.71</t>
+  </si>
+  <si>
+    <t>72.46</t>
+  </si>
+  <si>
+    <t>29.90</t>
+  </si>
+  <si>
+    <t>114.88</t>
+  </si>
+  <si>
+    <t>31.79</t>
+  </si>
+  <si>
+    <t>1.233,28</t>
+  </si>
+  <si>
+    <t>112.25</t>
+  </si>
+  <si>
+    <t>15.63</t>
+  </si>
+  <si>
+    <t>118.78</t>
+  </si>
+  <si>
+    <t>75.02</t>
+  </si>
+  <si>
+    <t>13,12</t>
+  </si>
+  <si>
+    <t>101,23</t>
+  </si>
+  <si>
+    <t>17.85</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>136,26</t>
+  </si>
+  <si>
+    <t>145,62</t>
+  </si>
+  <si>
+    <t>16.25</t>
+  </si>
+  <si>
+    <t>26,07</t>
+  </si>
+  <si>
+    <t>310,02</t>
+  </si>
+  <si>
+    <t>96.22</t>
+  </si>
+  <si>
+    <t>177.39</t>
+  </si>
+  <si>
+    <t>140.89</t>
+  </si>
+  <si>
+    <t>73.68</t>
+  </si>
+  <si>
+    <t>296.65</t>
+  </si>
+  <si>
+    <t>126,51</t>
+  </si>
+  <si>
+    <t>27.94</t>
+  </si>
+  <si>
+    <t>27.11</t>
+  </si>
+  <si>
+    <t>36.23</t>
+  </si>
+  <si>
+    <t>13,00</t>
+  </si>
+  <si>
+    <t>117.00</t>
+  </si>
+  <si>
+    <t>112,57</t>
+  </si>
+  <si>
+    <t>273,32</t>
+  </si>
+  <si>
+    <t>36.99</t>
+  </si>
+  <si>
+    <t>70,41</t>
+  </si>
+  <si>
+    <t>231,.76</t>
+  </si>
+  <si>
+    <t>41,.61</t>
+  </si>
+  <si>
+    <t>24,64</t>
+  </si>
+  <si>
+    <t>146.25</t>
+  </si>
+  <si>
+    <t>300.45</t>
+  </si>
+  <si>
+    <t>13,62</t>
+  </si>
+  <si>
+    <t>222,07</t>
+  </si>
+  <si>
+    <t>82.14</t>
+  </si>
+  <si>
+    <t>26,60</t>
+  </si>
+  <si>
+    <t>95.42</t>
+  </si>
+  <si>
+    <t>25,20</t>
+  </si>
+  <si>
+    <t>45,40</t>
+  </si>
+  <si>
+    <t>52.21</t>
+  </si>
+  <si>
+    <t>124,80</t>
+  </si>
+  <si>
+    <t>67.96</t>
+  </si>
+  <si>
+    <t>15,60</t>
+  </si>
+  <si>
+    <t>20,29</t>
+  </si>
+  <si>
+    <t>62.94</t>
+  </si>
+  <si>
+    <t>11.28</t>
+  </si>
+  <si>
+    <t>39.64</t>
+  </si>
+  <si>
+    <t>98.49</t>
+  </si>
+  <si>
+    <t>107.19</t>
+  </si>
+  <si>
+    <t>161.76</t>
+  </si>
+  <si>
+    <t>165.13</t>
+  </si>
+  <si>
+    <t>164.34</t>
+  </si>
+  <si>
+    <t>3.57</t>
+  </si>
+  <si>
+    <t>24.74</t>
+  </si>
+  <si>
+    <t>.56</t>
+  </si>
+  <si>
+    <t>222,14</t>
+  </si>
+  <si>
+    <t>110,01</t>
+  </si>
+  <si>
+    <t>180.38</t>
+  </si>
+  <si>
+    <t>206,50</t>
+  </si>
+  <si>
+    <t>215,20</t>
+  </si>
+  <si>
+    <t>213,12</t>
+  </si>
+  <si>
+    <t>195,.10</t>
+  </si>
+  <si>
+    <t>332,80</t>
+  </si>
+  <si>
+    <t>215.78</t>
+  </si>
+  <si>
+    <t>522.25</t>
+  </si>
+  <si>
+    <t>235.28</t>
+  </si>
+  <si>
+    <t>131,61</t>
+  </si>
+  <si>
+    <t>3.26</t>
+  </si>
+  <si>
+    <t>113,85</t>
+  </si>
+  <si>
+    <t>158.40</t>
+  </si>
+  <si>
+    <t>214,29</t>
+  </si>
+  <si>
+    <t>52,16</t>
+  </si>
+  <si>
+    <t>72,14</t>
+  </si>
+  <si>
+    <t>122,90</t>
+  </si>
+  <si>
+    <t>215,.43</t>
+  </si>
+  <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t>512,30</t>
+  </si>
+  <si>
     <t>72,00</t>
   </si>
   <si>
-    <t>89.03</t>
-  </si>
-  <si>
-    <t>512,30</t>
-  </si>
-  <si>
-    <t>554.52</t>
-  </si>
-  <si>
-    <t>115.08</t>
-  </si>
-  <si>
-    <t>144,04</t>
-  </si>
-  <si>
-    <t>48.75</t>
-  </si>
-  <si>
-    <t>384.28</t>
-  </si>
-  <si>
-    <t>53.17</t>
-  </si>
-  <si>
-    <t>11.41</t>
-  </si>
-  <si>
-    <t>248.16</t>
-  </si>
-  <si>
-    <t>175.53</t>
-  </si>
-  <si>
-    <t>516.48</t>
-  </si>
-  <si>
-    <t>242.37</t>
-  </si>
-  <si>
-    <t>757.97</t>
-  </si>
-  <si>
-    <t>19.25</t>
-  </si>
-  <si>
-    <t>5.63</t>
-  </si>
-  <si>
-    <t>399.77</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
-    <t>19.90</t>
-  </si>
-  <si>
-    <t>86.57</t>
-  </si>
-  <si>
-    <t>447.21</t>
-  </si>
-  <si>
-    <t>11.52</t>
-  </si>
-  <si>
-    <t>19.77</t>
-  </si>
-  <si>
-    <t>21.19</t>
-  </si>
-  <si>
-    <t>78.24</t>
-  </si>
-  <si>
-    <t>215.43</t>
-  </si>
-  <si>
-    <t>61.93</t>
-  </si>
-  <si>
-    <t>16.00</t>
-  </si>
-  <si>
-    <t>189.24</t>
-  </si>
-  <si>
-    <t>78.30</t>
-  </si>
-  <si>
-    <t>8.64</t>
-  </si>
-  <si>
-    <t>207.76</t>
-  </si>
-  <si>
-    <t>384.64</t>
-  </si>
-  <si>
-    <t>112.77</t>
-  </si>
-  <si>
-    <t>7.92</t>
-  </si>
-  <si>
-    <t>45.24</t>
-  </si>
-  <si>
-    <t>122.90</t>
-  </si>
-  <si>
-    <t>300.08</t>
-  </si>
-  <si>
-    <t>76.98</t>
-  </si>
-  <si>
-    <t>8.51</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>251.28</t>
-  </si>
-  <si>
-    <t>127.72</t>
-  </si>
-  <si>
-    <t>19.29</t>
-  </si>
-  <si>
-    <t>61.80</t>
-  </si>
-  <si>
-    <t>472.08</t>
-  </si>
-  <si>
-    <t>252.88</t>
-  </si>
-  <si>
-    <t>121.32</t>
-  </si>
-  <si>
-    <t>171.40</t>
-  </si>
-  <si>
-    <t>46.41</t>
-  </si>
-  <si>
-    <t>255.64</t>
-  </si>
-  <si>
-    <t>72.14</t>
-  </si>
-  <si>
-    <t>45.23</t>
-  </si>
-  <si>
-    <t>65.50</t>
-  </si>
-  <si>
-    <t>74.02</t>
-  </si>
-  <si>
-    <t>130,20</t>
-  </si>
-  <si>
-    <t>90.80</t>
-  </si>
-  <si>
-    <t>5.50</t>
-  </si>
-  <si>
-    <t>181.98</t>
-  </si>
-  <si>
-    <t>64.66</t>
-  </si>
-  <si>
-    <t>13,20</t>
-  </si>
-  <si>
-    <t>386.68</t>
-  </si>
-  <si>
-    <t>10.27</t>
-  </si>
-  <si>
-    <t>106.54</t>
-  </si>
-  <si>
-    <t>52.16</t>
-  </si>
-  <si>
-    <t>20.93</t>
-  </si>
-  <si>
-    <t>3.37</t>
-  </si>
-  <si>
-    <t>188.28</t>
-  </si>
-  <si>
-    <t>78.45</t>
-  </si>
-  <si>
-    <t>83.20</t>
-  </si>
-  <si>
-    <t>87.66</t>
-  </si>
-  <si>
-    <t>131.61</t>
-  </si>
-  <si>
-    <t>446.31</t>
-  </si>
-  <si>
-    <t>332.80</t>
-  </si>
-  <si>
-    <t>166.40</t>
-  </si>
-  <si>
-    <t>195.54</t>
-  </si>
-  <si>
-    <t>212.31</t>
-  </si>
-  <si>
-    <t>14.85</t>
-  </si>
-  <si>
-    <t>16.03</t>
-  </si>
-  <si>
-    <t>100.88</t>
-  </si>
-  <si>
-    <t>108.48</t>
-  </si>
-  <si>
-    <t>522.25</t>
-  </si>
-  <si>
-    <t>107.12</t>
-  </si>
-  <si>
-    <t>66.30</t>
-  </si>
-  <si>
-    <t>22.37</t>
-  </si>
-  <si>
-    <t>66.50</t>
-  </si>
-  <si>
-    <t>51.59</t>
-  </si>
-  <si>
-    <t>6.74</t>
-  </si>
-  <si>
-    <t>33.91</t>
-  </si>
-  <si>
-    <t>195.10</t>
-  </si>
-  <si>
-    <t>213.12</t>
-  </si>
-  <si>
-    <t>184.32</t>
-  </si>
-  <si>
-    <t>215,20</t>
-  </si>
-  <si>
-    <t>139.54</t>
-  </si>
-  <si>
-    <t>2.75</t>
-  </si>
-  <si>
-    <t>10.51</t>
-  </si>
-  <si>
-    <t>239.55</t>
-  </si>
-  <si>
-    <t>94.03</t>
-  </si>
-  <si>
-    <t>206,50</t>
-  </si>
-  <si>
-    <t>204.63</t>
-  </si>
-  <si>
-    <t>194.70</t>
-  </si>
-  <si>
-    <t>52.27</t>
-  </si>
-  <si>
-    <t>44.32</t>
-  </si>
-  <si>
-    <t>74.04</t>
-  </si>
-  <si>
-    <t>110.01</t>
-  </si>
-  <si>
-    <t>65.37</t>
-  </si>
-  <si>
-    <t>222.14</t>
-  </si>
-  <si>
-    <t>296,56</t>
-  </si>
-  <si>
-    <t>293.19</t>
-  </si>
-  <si>
-    <t>363.23</t>
-  </si>
-  <si>
-    <t>418.25</t>
-  </si>
-  <si>
-    <t>40.44</t>
-  </si>
-  <si>
-    <t>61.05</t>
-  </si>
-  <si>
-    <t>3.57</t>
-  </si>
-  <si>
-    <t>231.00</t>
-  </si>
-  <si>
-    <t>22.07</t>
-  </si>
-  <si>
-    <t>54.48</t>
-  </si>
-  <si>
-    <t>165.13</t>
-  </si>
-  <si>
-    <t>157.50</t>
-  </si>
-  <si>
-    <t>98.49</t>
-  </si>
-  <si>
-    <t>45.50</t>
-  </si>
-  <si>
-    <t>11.28</t>
-  </si>
-  <si>
-    <t>225.80</t>
-  </si>
-  <si>
-    <t>204.48</t>
-  </si>
-  <si>
-    <t>55.64</t>
-  </si>
-  <si>
-    <t>15.60</t>
-  </si>
-  <si>
-    <t>103.81</t>
-  </si>
-  <si>
-    <t>124,80</t>
-  </si>
-  <si>
-    <t>5.28</t>
-  </si>
-  <si>
-    <t>41.21</t>
-  </si>
-  <si>
-    <t>98.56</t>
-  </si>
-  <si>
-    <t>52,.21</t>
-  </si>
-  <si>
-    <t>69.67</t>
-  </si>
-  <si>
-    <t>25.20</t>
-  </si>
-  <si>
-    <t>39.12</t>
-  </si>
-  <si>
-    <t>95.42</t>
-  </si>
-  <si>
-    <t>5662</t>
-  </si>
-  <si>
-    <t>26,60</t>
-  </si>
-  <si>
-    <t>222.07</t>
-  </si>
-  <si>
-    <t>169.80</t>
-  </si>
-  <si>
-    <t>150.39</t>
-  </si>
-  <si>
-    <t>300.45</t>
-  </si>
-  <si>
-    <t>16.73</t>
-  </si>
-  <si>
-    <t>13.48</t>
-  </si>
-  <si>
-    <t>41.60</t>
-  </si>
-  <si>
-    <t>146.25</t>
-  </si>
-  <si>
-    <t>41.61</t>
-  </si>
-  <si>
-    <t>32.50</t>
-  </si>
-  <si>
-    <t>231.76</t>
-  </si>
-  <si>
-    <t>123.89</t>
-  </si>
-  <si>
-    <t>488.43</t>
-  </si>
-  <si>
-    <t>26.36</t>
-  </si>
-  <si>
-    <t>70.41</t>
-  </si>
-  <si>
-    <t>36.99</t>
-  </si>
-  <si>
-    <t>117.00</t>
-  </si>
-  <si>
-    <t>13.00</t>
-  </si>
-  <si>
-    <t>27.94</t>
-  </si>
-  <si>
-    <t>256.49</t>
-  </si>
-  <si>
-    <t>68.25</t>
-  </si>
-  <si>
-    <t>669.82</t>
-  </si>
-  <si>
-    <t>421.35</t>
-  </si>
-  <si>
-    <t>167.41</t>
-  </si>
-  <si>
-    <t>177.39</t>
-  </si>
-  <si>
-    <t>98.03</t>
-  </si>
-  <si>
-    <t>66.97</t>
-  </si>
-  <si>
-    <t>43.09</t>
-  </si>
-  <si>
-    <t>42.71</t>
-  </si>
-  <si>
-    <t>33.25</t>
-  </si>
-  <si>
-    <t>52.24</t>
-  </si>
-  <si>
-    <t>80.88</t>
-  </si>
-  <si>
-    <t>20.53</t>
-  </si>
-  <si>
-    <t>65.36</t>
-  </si>
-  <si>
-    <t>83.71</t>
-  </si>
-  <si>
-    <t>95.78</t>
-  </si>
-  <si>
-    <t>262.86</t>
-  </si>
-  <si>
-    <t>337.20</t>
-  </si>
-  <si>
-    <t>18.49</t>
-  </si>
-  <si>
-    <t>187.36</t>
-  </si>
-  <si>
-    <t>101.23</t>
-  </si>
-  <si>
-    <t>13.12</t>
-  </si>
-  <si>
-    <t>124.46</t>
-  </si>
-  <si>
-    <t>5.64</t>
-  </si>
-  <si>
-    <t>53.92</t>
-  </si>
-  <si>
-    <t>29.25</t>
-  </si>
-  <si>
-    <t>204.78</t>
-  </si>
-  <si>
-    <t>21.74</t>
-  </si>
-  <si>
-    <t>235.90</t>
-  </si>
-  <si>
-    <t>48.71</t>
-  </si>
-  <si>
-    <t>72.46</t>
-  </si>
-  <si>
-    <t>29.90</t>
-  </si>
-  <si>
-    <t>114.88</t>
-  </si>
-  <si>
-    <t>31.79</t>
-  </si>
-  <si>
-    <t>1.233.28</t>
-  </si>
-  <si>
-    <t>112.25</t>
-  </si>
-  <si>
-    <t>15.63</t>
-  </si>
-  <si>
-    <t>118.78</t>
-  </si>
-  <si>
-    <t>57.29</t>
-  </si>
-  <si>
-    <t>75.02</t>
+    <t>668</t>
   </si>
   <si>
     <t>Lançamento visível no Consinco mas NÃO consta na planilha do Excel</t>
@@ -1821,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C431"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1840,10 +2578,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>433</v>
       </c>
       <c r="C2" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1851,10 +2589,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>434</v>
       </c>
       <c r="C3" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1862,10 +2600,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>435</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1873,10 +2611,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>436</v>
       </c>
       <c r="C5" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1884,10 +2622,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>437</v>
       </c>
       <c r="C6" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1895,10 +2633,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>438</v>
       </c>
       <c r="C7" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1906,10 +2644,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>263</v>
+        <v>436</v>
       </c>
       <c r="C8" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1917,10 +2655,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>439</v>
       </c>
       <c r="C9" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1928,10 +2666,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>265</v>
+        <v>440</v>
       </c>
       <c r="C10" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1939,10 +2677,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>441</v>
       </c>
       <c r="C11" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1950,10 +2688,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>442</v>
       </c>
       <c r="C12" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1961,10 +2699,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="C13" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1972,10 +2710,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>444</v>
       </c>
       <c r="C14" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1983,10 +2721,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>445</v>
       </c>
       <c r="C15" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1994,10 +2732,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>446</v>
       </c>
       <c r="C16" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2005,10 +2743,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
+        <v>447</v>
       </c>
       <c r="C17" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2016,10 +2754,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>273</v>
+        <v>448</v>
       </c>
       <c r="C18" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2027,10 +2765,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>449</v>
       </c>
       <c r="C19" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2038,10 +2776,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>450</v>
       </c>
       <c r="C20" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2049,10 +2787,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>451</v>
       </c>
       <c r="C21" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2060,10 +2798,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>277</v>
+        <v>452</v>
       </c>
       <c r="C22" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2071,10 +2809,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>278</v>
+        <v>453</v>
       </c>
       <c r="C23" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2082,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>454</v>
       </c>
       <c r="C24" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2093,10 +2831,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="C25" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2104,10 +2842,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>280</v>
+        <v>455</v>
       </c>
       <c r="C26" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2115,10 +2853,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>281</v>
+        <v>456</v>
       </c>
       <c r="C27" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2126,10 +2864,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>282</v>
+        <v>457</v>
       </c>
       <c r="C28" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2137,10 +2875,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>283</v>
+        <v>458</v>
       </c>
       <c r="C29" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2148,10 +2886,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>284</v>
+        <v>459</v>
       </c>
       <c r="C30" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2159,10 +2897,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>285</v>
+        <v>460</v>
       </c>
       <c r="C31" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2170,10 +2908,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>286</v>
+        <v>461</v>
       </c>
       <c r="C32" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2181,10 +2919,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>462</v>
       </c>
       <c r="C33" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2192,10 +2930,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>288</v>
+        <v>463</v>
       </c>
       <c r="C34" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2203,10 +2941,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>464</v>
       </c>
       <c r="C35" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2214,10 +2952,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>290</v>
+        <v>465</v>
       </c>
       <c r="C36" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2225,10 +2963,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>291</v>
+        <v>466</v>
       </c>
       <c r="C37" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2236,10 +2974,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>292</v>
+        <v>467</v>
       </c>
       <c r="C38" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2247,10 +2985,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>468</v>
       </c>
       <c r="C39" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2258,10 +2996,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>294</v>
+        <v>469</v>
       </c>
       <c r="C40" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2269,10 +3007,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>295</v>
+        <v>470</v>
       </c>
       <c r="C41" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2280,10 +3018,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>296</v>
+        <v>471</v>
       </c>
       <c r="C42" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2291,10 +3029,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>472</v>
       </c>
       <c r="C43" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2302,10 +3040,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>298</v>
+        <v>473</v>
       </c>
       <c r="C44" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2313,10 +3051,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>299</v>
+        <v>474</v>
       </c>
       <c r="C45" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2324,10 +3062,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>300</v>
+        <v>475</v>
       </c>
       <c r="C46" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2335,10 +3073,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="C47" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2346,10 +3084,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>301</v>
+        <v>476</v>
       </c>
       <c r="C48" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -2357,10 +3095,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>302</v>
+        <v>477</v>
       </c>
       <c r="C49" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -2368,10 +3106,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>303</v>
+        <v>478</v>
       </c>
       <c r="C50" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2379,10 +3117,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>304</v>
+        <v>479</v>
       </c>
       <c r="C51" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2390,10 +3128,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="C52" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2401,10 +3139,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>305</v>
+        <v>480</v>
       </c>
       <c r="C53" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2412,10 +3150,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>306</v>
+        <v>481</v>
       </c>
       <c r="C54" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2423,10 +3161,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>307</v>
+        <v>482</v>
       </c>
       <c r="C55" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2434,10 +3172,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>308</v>
+        <v>483</v>
       </c>
       <c r="C56" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2445,10 +3183,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>309</v>
+        <v>484</v>
       </c>
       <c r="C57" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2456,10 +3194,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>310</v>
+        <v>485</v>
       </c>
       <c r="C58" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2467,10 +3205,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>486</v>
       </c>
       <c r="C59" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2478,10 +3216,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>312</v>
+        <v>487</v>
       </c>
       <c r="C60" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2489,10 +3227,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>313</v>
+        <v>488</v>
       </c>
       <c r="C61" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2500,10 +3238,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>314</v>
+        <v>489</v>
       </c>
       <c r="C62" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2511,10 +3249,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>315</v>
+        <v>490</v>
       </c>
       <c r="C63" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -2522,10 +3260,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>316</v>
+        <v>491</v>
       </c>
       <c r="C64" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2533,10 +3271,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>317</v>
+        <v>492</v>
       </c>
       <c r="C65" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2544,10 +3282,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>283</v>
+        <v>458</v>
       </c>
       <c r="C66" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2555,10 +3293,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>318</v>
+        <v>493</v>
       </c>
       <c r="C67" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -2566,10 +3304,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>319</v>
+        <v>494</v>
       </c>
       <c r="C68" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2577,10 +3315,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="C69" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2588,10 +3326,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>320</v>
+        <v>495</v>
       </c>
       <c r="C70" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -2599,10 +3337,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>321</v>
+        <v>496</v>
       </c>
       <c r="C71" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -2610,10 +3348,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>322</v>
+        <v>497</v>
       </c>
       <c r="C72" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -2621,10 +3359,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>323</v>
+        <v>498</v>
       </c>
       <c r="C73" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -2632,10 +3370,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>324</v>
+        <v>499</v>
       </c>
       <c r="C74" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -2643,10 +3381,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="C75" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -2654,10 +3392,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>326</v>
+        <v>501</v>
       </c>
       <c r="C76" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -2665,10 +3403,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>327</v>
+        <v>502</v>
       </c>
       <c r="C77" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2676,10 +3414,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>328</v>
+        <v>503</v>
       </c>
       <c r="C78" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2687,10 +3425,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>329</v>
+        <v>504</v>
       </c>
       <c r="C79" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2698,10 +3436,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>330</v>
+        <v>505</v>
       </c>
       <c r="C80" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2709,10 +3447,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>331</v>
+        <v>506</v>
       </c>
       <c r="C81" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2720,10 +3458,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>332</v>
+        <v>507</v>
       </c>
       <c r="C82" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2731,10 +3469,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>333</v>
+        <v>508</v>
       </c>
       <c r="C83" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2742,10 +3480,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>334</v>
+        <v>509</v>
       </c>
       <c r="C84" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2753,10 +3491,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>335</v>
+        <v>510</v>
       </c>
       <c r="C85" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2764,10 +3502,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>336</v>
+        <v>511</v>
       </c>
       <c r="C86" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2775,10 +3513,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>337</v>
+        <v>512</v>
       </c>
       <c r="C87" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2786,10 +3524,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>338</v>
+        <v>513</v>
       </c>
       <c r="C88" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2797,10 +3535,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>339</v>
+        <v>514</v>
       </c>
       <c r="C89" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2808,10 +3546,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>340</v>
+        <v>515</v>
       </c>
       <c r="C90" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2819,10 +3557,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="C91" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2830,10 +3568,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>342</v>
+        <v>517</v>
       </c>
       <c r="C92" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2841,10 +3579,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>343</v>
+        <v>518</v>
       </c>
       <c r="C93" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2852,10 +3590,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>344</v>
+        <v>519</v>
       </c>
       <c r="C94" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2863,10 +3601,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>345</v>
+        <v>520</v>
       </c>
       <c r="C95" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2874,10 +3612,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>346</v>
+        <v>521</v>
       </c>
       <c r="C96" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2885,10 +3623,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>347</v>
+        <v>522</v>
       </c>
       <c r="C97" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2896,10 +3634,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>348</v>
+        <v>523</v>
       </c>
       <c r="C98" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2907,10 +3645,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>349</v>
+        <v>524</v>
       </c>
       <c r="C99" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2918,10 +3656,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>350</v>
+        <v>525</v>
       </c>
       <c r="C100" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2929,10 +3667,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>351</v>
+        <v>526</v>
       </c>
       <c r="C101" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2940,10 +3678,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>352</v>
+        <v>527</v>
       </c>
       <c r="C102" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2951,10 +3689,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>353</v>
+        <v>528</v>
       </c>
       <c r="C103" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2962,10 +3700,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>354</v>
+        <v>529</v>
       </c>
       <c r="C104" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2973,10 +3711,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>355</v>
+        <v>530</v>
       </c>
       <c r="C105" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2984,10 +3722,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>356</v>
+        <v>531</v>
       </c>
       <c r="C106" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2995,10 +3733,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>357</v>
+        <v>532</v>
       </c>
       <c r="C107" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -3006,10 +3744,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>358</v>
+        <v>533</v>
       </c>
       <c r="C108" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3017,10 +3755,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>359</v>
+        <v>534</v>
       </c>
       <c r="C109" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -3028,10 +3766,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>360</v>
+        <v>535</v>
       </c>
       <c r="C110" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -3039,10 +3777,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>360</v>
+        <v>536</v>
       </c>
       <c r="C111" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3050,10 +3788,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>361</v>
+        <v>537</v>
       </c>
       <c r="C112" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3061,10 +3799,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>362</v>
+        <v>538</v>
       </c>
       <c r="C113" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3072,10 +3810,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>363</v>
+        <v>538</v>
       </c>
       <c r="C114" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3083,10 +3821,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>364</v>
+        <v>539</v>
       </c>
       <c r="C115" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3094,10 +3832,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>365</v>
+        <v>540</v>
       </c>
       <c r="C116" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3105,10 +3843,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>359</v>
+        <v>541</v>
       </c>
       <c r="C117" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -3116,10 +3854,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="C118" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3127,10 +3865,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
+        <v>543</v>
       </c>
       <c r="C119" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3138,10 +3876,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>367</v>
+        <v>534</v>
       </c>
       <c r="C120" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3149,10 +3887,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>368</v>
+        <v>544</v>
       </c>
       <c r="C121" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3160,10 +3898,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="C122" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3171,10 +3909,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>370</v>
+        <v>545</v>
       </c>
       <c r="C123" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3182,10 +3920,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>371</v>
+        <v>546</v>
       </c>
       <c r="C124" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3193,10 +3931,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>372</v>
+        <v>547</v>
       </c>
       <c r="C125" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3204,10 +3942,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>373</v>
+        <v>548</v>
       </c>
       <c r="C126" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3215,10 +3953,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="s">
-        <v>374</v>
+        <v>549</v>
       </c>
       <c r="C127" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3226,10 +3964,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="s">
-        <v>375</v>
+        <v>550</v>
       </c>
       <c r="C128" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3237,10 +3975,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>366</v>
+        <v>551</v>
       </c>
       <c r="C129" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3248,10 +3986,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>376</v>
+        <v>552</v>
       </c>
       <c r="C130" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3259,10 +3997,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>377</v>
+        <v>544</v>
       </c>
       <c r="C131" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3270,10 +4008,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="s">
-        <v>378</v>
+        <v>553</v>
       </c>
       <c r="C132" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3281,10 +4019,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="s">
-        <v>379</v>
+        <v>554</v>
       </c>
       <c r="C133" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3292,10 +4030,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>380</v>
+        <v>555</v>
       </c>
       <c r="C134" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3303,18 +4041,21 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>381</v>
+        <v>556</v>
       </c>
       <c r="C135" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>137</v>
       </c>
+      <c r="B136" t="s">
+        <v>557</v>
+      </c>
       <c r="C136" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3322,10 +4063,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="s">
-        <v>382</v>
+        <v>558</v>
       </c>
       <c r="C137" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3333,10 +4074,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>559</v>
       </c>
       <c r="C138" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3344,10 +4085,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>384</v>
+        <v>560</v>
       </c>
       <c r="C139" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3355,10 +4096,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
-        <v>385</v>
+        <v>561</v>
       </c>
       <c r="C140" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3366,10 +4107,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>386</v>
+        <v>562</v>
       </c>
       <c r="C141" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3377,10 +4118,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="s">
-        <v>387</v>
+        <v>563</v>
       </c>
       <c r="C142" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3388,10 +4129,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>388</v>
+        <v>564</v>
       </c>
       <c r="C143" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3399,10 +4140,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>389</v>
+        <v>565</v>
       </c>
       <c r="C144" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3410,10 +4151,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>390</v>
+        <v>566</v>
       </c>
       <c r="C145" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3421,10 +4162,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>391</v>
+        <v>567</v>
       </c>
       <c r="C146" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3432,10 +4173,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="s">
-        <v>392</v>
+        <v>568</v>
       </c>
       <c r="C147" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3443,10 +4184,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>393</v>
+        <v>569</v>
       </c>
       <c r="C148" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3454,10 +4195,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>394</v>
+        <v>570</v>
       </c>
       <c r="C149" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -3465,10 +4206,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="s">
-        <v>395</v>
+        <v>571</v>
       </c>
       <c r="C150" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -3476,10 +4217,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>396</v>
+        <v>572</v>
       </c>
       <c r="C151" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -3487,10 +4228,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>397</v>
+        <v>573</v>
       </c>
       <c r="C152" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -3498,10 +4239,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="s">
-        <v>398</v>
+        <v>574</v>
       </c>
       <c r="C153" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -3509,10 +4250,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="s">
-        <v>399</v>
+        <v>575</v>
       </c>
       <c r="C154" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -3520,10 +4261,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>400</v>
+        <v>576</v>
       </c>
       <c r="C155" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -3531,10 +4272,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="s">
-        <v>401</v>
+        <v>577</v>
       </c>
       <c r="C156" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -3542,10 +4283,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="s">
-        <v>402</v>
+        <v>578</v>
       </c>
       <c r="C157" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -3553,10 +4294,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
-        <v>403</v>
+        <v>579</v>
       </c>
       <c r="C158" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -3564,10 +4305,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>404</v>
+        <v>580</v>
       </c>
       <c r="C159" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -3575,10 +4316,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>405</v>
+        <v>581</v>
       </c>
       <c r="C160" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -3586,10 +4327,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>359</v>
+        <v>582</v>
       </c>
       <c r="C161" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -3597,10 +4338,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>406</v>
+        <v>583</v>
       </c>
       <c r="C162" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -3608,10 +4349,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="s">
-        <v>407</v>
+        <v>584</v>
       </c>
       <c r="C163" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -3619,10 +4360,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="s">
-        <v>408</v>
+        <v>585</v>
       </c>
       <c r="C164" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -3630,10 +4371,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>409</v>
+        <v>586</v>
       </c>
       <c r="C165" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -3641,10 +4382,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>410</v>
+        <v>587</v>
       </c>
       <c r="C166" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -3652,10 +4393,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>411</v>
+        <v>588</v>
       </c>
       <c r="C167" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -3663,10 +4404,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>412</v>
+        <v>589</v>
       </c>
       <c r="C168" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -3674,10 +4415,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="s">
-        <v>413</v>
+        <v>590</v>
       </c>
       <c r="C169" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -3685,10 +4426,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="s">
-        <v>414</v>
+        <v>591</v>
       </c>
       <c r="C170" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -3696,10 +4437,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="s">
-        <v>415</v>
+        <v>592</v>
       </c>
       <c r="C171" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3707,10 +4448,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="s">
-        <v>416</v>
+        <v>593</v>
       </c>
       <c r="C172" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -3718,10 +4459,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="s">
-        <v>417</v>
+        <v>594</v>
       </c>
       <c r="C173" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -3729,10 +4470,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="s">
-        <v>418</v>
+        <v>595</v>
       </c>
       <c r="C174" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3740,10 +4481,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="s">
-        <v>419</v>
+        <v>596</v>
       </c>
       <c r="C175" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -3751,10 +4492,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="s">
-        <v>420</v>
+        <v>597</v>
       </c>
       <c r="C176" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -3762,10 +4503,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="s">
-        <v>421</v>
+        <v>598</v>
       </c>
       <c r="C177" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3773,10 +4514,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="s">
-        <v>422</v>
+        <v>599</v>
       </c>
       <c r="C178" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3784,10 +4525,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="s">
-        <v>423</v>
+        <v>600</v>
       </c>
       <c r="C179" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3795,10 +4536,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="s">
-        <v>424</v>
+        <v>601</v>
       </c>
       <c r="C180" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -3806,10 +4547,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="s">
-        <v>425</v>
+        <v>602</v>
       </c>
       <c r="C181" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3817,10 +4558,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="s">
-        <v>426</v>
+        <v>603</v>
       </c>
       <c r="C182" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3828,10 +4569,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="s">
-        <v>427</v>
+        <v>604</v>
       </c>
       <c r="C183" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3839,10 +4580,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="s">
-        <v>428</v>
+        <v>605</v>
       </c>
       <c r="C184" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3850,10 +4591,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="s">
-        <v>429</v>
+        <v>606</v>
       </c>
       <c r="C185" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3861,10 +4602,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="s">
-        <v>430</v>
+        <v>607</v>
       </c>
       <c r="C186" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3872,10 +4613,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="s">
-        <v>431</v>
+        <v>608</v>
       </c>
       <c r="C187" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3883,10 +4624,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="s">
-        <v>432</v>
+        <v>609</v>
       </c>
       <c r="C188" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3894,10 +4635,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="s">
-        <v>433</v>
+        <v>610</v>
       </c>
       <c r="C189" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3905,10 +4646,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="s">
-        <v>434</v>
+        <v>611</v>
       </c>
       <c r="C190" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3916,10 +4657,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="s">
-        <v>435</v>
+        <v>612</v>
       </c>
       <c r="C191" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -3927,10 +4668,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="s">
-        <v>436</v>
+        <v>613</v>
       </c>
       <c r="C192" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -3938,10 +4679,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="s">
-        <v>437</v>
+        <v>614</v>
       </c>
       <c r="C193" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3949,10 +4690,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="s">
-        <v>438</v>
+        <v>615</v>
       </c>
       <c r="C194" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3960,10 +4701,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="s">
-        <v>439</v>
+        <v>616</v>
       </c>
       <c r="C195" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3971,10 +4712,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="s">
-        <v>440</v>
+        <v>617</v>
       </c>
       <c r="C196" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3982,10 +4723,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="s">
-        <v>441</v>
+        <v>618</v>
       </c>
       <c r="C197" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -3993,10 +4734,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>442</v>
+        <v>619</v>
       </c>
       <c r="C198" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -4004,10 +4745,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="s">
-        <v>443</v>
+        <v>620</v>
       </c>
       <c r="C199" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -4015,10 +4756,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="s">
-        <v>444</v>
+        <v>621</v>
       </c>
       <c r="C200" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -4026,10 +4767,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>445</v>
+        <v>622</v>
       </c>
       <c r="C201" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -4037,10 +4778,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="s">
-        <v>446</v>
+        <v>623</v>
       </c>
       <c r="C202" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -4048,10 +4789,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="s">
-        <v>436</v>
+        <v>624</v>
       </c>
       <c r="C203" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -4059,10 +4800,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="s">
-        <v>447</v>
+        <v>625</v>
       </c>
       <c r="C204" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -4070,10 +4811,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="s">
-        <v>448</v>
+        <v>626</v>
       </c>
       <c r="C205" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -4081,10 +4822,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="s">
-        <v>449</v>
+        <v>627</v>
       </c>
       <c r="C206" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -4092,10 +4833,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="s">
-        <v>450</v>
+        <v>628</v>
       </c>
       <c r="C207" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -4103,10 +4844,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>451</v>
+        <v>629</v>
       </c>
       <c r="C208" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -4114,10 +4855,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="s">
-        <v>452</v>
+        <v>630</v>
       </c>
       <c r="C209" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -4125,10 +4866,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="s">
-        <v>453</v>
+        <v>631</v>
       </c>
       <c r="C210" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -4136,10 +4877,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="s">
-        <v>454</v>
+        <v>632</v>
       </c>
       <c r="C211" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -4147,10 +4888,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="s">
-        <v>455</v>
+        <v>589</v>
       </c>
       <c r="C212" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -4158,10 +4899,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="s">
-        <v>456</v>
+        <v>633</v>
       </c>
       <c r="C213" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -4169,10 +4910,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="s">
-        <v>457</v>
+        <v>634</v>
       </c>
       <c r="C214" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -4180,10 +4921,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="s">
-        <v>458</v>
+        <v>635</v>
       </c>
       <c r="C215" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -4191,10 +4932,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="s">
-        <v>459</v>
+        <v>636</v>
       </c>
       <c r="C216" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -4202,10 +4943,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="s">
-        <v>460</v>
+        <v>637</v>
       </c>
       <c r="C217" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -4213,10 +4954,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="s">
-        <v>461</v>
+        <v>638</v>
       </c>
       <c r="C218" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -4224,10 +4965,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="s">
-        <v>462</v>
+        <v>639</v>
       </c>
       <c r="C219" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -4235,10 +4976,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="s">
-        <v>462</v>
+        <v>534</v>
       </c>
       <c r="C220" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -4246,10 +4987,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="s">
-        <v>463</v>
+        <v>640</v>
       </c>
       <c r="C221" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -4257,10 +4998,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="s">
-        <v>464</v>
+        <v>641</v>
       </c>
       <c r="C222" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -4268,10 +5009,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="s">
-        <v>465</v>
+        <v>642</v>
       </c>
       <c r="C223" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -4279,10 +5020,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="s">
-        <v>466</v>
+        <v>643</v>
       </c>
       <c r="C224" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -4290,10 +5031,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="s">
-        <v>467</v>
+        <v>644</v>
       </c>
       <c r="C225" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -4301,10 +5042,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="s">
-        <v>359</v>
+        <v>588</v>
       </c>
       <c r="C226" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -4312,21 +5053,18 @@
         <v>228</v>
       </c>
       <c r="B227" t="s">
-        <v>468</v>
+        <v>645</v>
       </c>
       <c r="C227" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
         <v>229</v>
       </c>
-      <c r="B228" t="s">
-        <v>469</v>
-      </c>
       <c r="C228" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -4334,10 +5072,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="s">
-        <v>470</v>
+        <v>646</v>
       </c>
       <c r="C229" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -4345,10 +5083,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="s">
-        <v>471</v>
+        <v>557</v>
       </c>
       <c r="C230" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -4356,10 +5094,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="s">
-        <v>472</v>
+        <v>647</v>
       </c>
       <c r="C231" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -4367,10 +5105,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="s">
-        <v>404</v>
+        <v>648</v>
       </c>
       <c r="C232" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -4378,10 +5116,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="s">
-        <v>473</v>
+        <v>649</v>
       </c>
       <c r="C233" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -4389,10 +5127,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="s">
-        <v>474</v>
+        <v>650</v>
       </c>
       <c r="C234" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -4400,10 +5138,10 @@
         <v>236</v>
       </c>
       <c r="B235" t="s">
-        <v>475</v>
+        <v>651</v>
       </c>
       <c r="C235" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -4411,10 +5149,10 @@
         <v>237</v>
       </c>
       <c r="B236" t="s">
-        <v>380</v>
+        <v>652</v>
       </c>
       <c r="C236" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -4422,10 +5160,10 @@
         <v>238</v>
       </c>
       <c r="B237" t="s">
-        <v>476</v>
+        <v>653</v>
       </c>
       <c r="C237" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -4433,10 +5171,10 @@
         <v>239</v>
       </c>
       <c r="B238" t="s">
-        <v>477</v>
+        <v>654</v>
       </c>
       <c r="C238" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -4444,10 +5182,10 @@
         <v>240</v>
       </c>
       <c r="B239" t="s">
-        <v>478</v>
+        <v>655</v>
       </c>
       <c r="C239" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -4455,10 +5193,10 @@
         <v>241</v>
       </c>
       <c r="B240" t="s">
-        <v>479</v>
+        <v>656</v>
       </c>
       <c r="C240" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -4466,10 +5204,10 @@
         <v>242</v>
       </c>
       <c r="B241" t="s">
-        <v>480</v>
+        <v>646</v>
       </c>
       <c r="C241" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -4477,10 +5215,10 @@
         <v>243</v>
       </c>
       <c r="B242" t="s">
-        <v>481</v>
+        <v>647</v>
       </c>
       <c r="C242" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -4488,10 +5226,10 @@
         <v>244</v>
       </c>
       <c r="B243" t="s">
-        <v>482</v>
+        <v>657</v>
       </c>
       <c r="C243" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -4499,10 +5237,10 @@
         <v>245</v>
       </c>
       <c r="B244" t="s">
-        <v>483</v>
+        <v>595</v>
       </c>
       <c r="C244" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -4510,10 +5248,10 @@
         <v>246</v>
       </c>
       <c r="B245" t="s">
-        <v>484</v>
+        <v>658</v>
       </c>
       <c r="C245" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -4521,10 +5259,10 @@
         <v>247</v>
       </c>
       <c r="B246" t="s">
-        <v>485</v>
+        <v>659</v>
       </c>
       <c r="C246" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -4532,10 +5270,10 @@
         <v>248</v>
       </c>
       <c r="B247" t="s">
-        <v>475</v>
+        <v>609</v>
       </c>
       <c r="C247" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -4543,10 +5281,10 @@
         <v>249</v>
       </c>
       <c r="B248" t="s">
-        <v>476</v>
+        <v>660</v>
       </c>
       <c r="C248" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -4554,10 +5292,10 @@
         <v>250</v>
       </c>
       <c r="B249" t="s">
-        <v>486</v>
+        <v>659</v>
       </c>
       <c r="C249" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -4565,10 +5303,10 @@
         <v>251</v>
       </c>
       <c r="B250" t="s">
-        <v>437</v>
+        <v>658</v>
       </c>
       <c r="C250" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -4576,10 +5314,10 @@
         <v>252</v>
       </c>
       <c r="B251" t="s">
-        <v>487</v>
+        <v>652</v>
       </c>
       <c r="C251" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -4587,10 +5325,10 @@
         <v>253</v>
       </c>
       <c r="B252" t="s">
-        <v>488</v>
+        <v>648</v>
       </c>
       <c r="C252" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -4598,10 +5336,10 @@
         <v>254</v>
       </c>
       <c r="B253" t="s">
-        <v>489</v>
+        <v>557</v>
       </c>
       <c r="C253" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -4609,10 +5347,10 @@
         <v>255</v>
       </c>
       <c r="B254" t="s">
-        <v>490</v>
+        <v>661</v>
       </c>
       <c r="C254" t="s">
-        <v>491</v>
+        <v>737</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -4620,10 +5358,1937 @@
         <v>256</v>
       </c>
       <c r="B255" t="s">
-        <v>485</v>
+        <v>662</v>
       </c>
       <c r="C255" t="s">
-        <v>491</v>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" t="s">
+        <v>257</v>
+      </c>
+      <c r="B256" t="s">
+        <v>642</v>
+      </c>
+      <c r="C256" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
+        <v>258</v>
+      </c>
+      <c r="B257" t="s">
+        <v>640</v>
+      </c>
+      <c r="C257" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>259</v>
+      </c>
+      <c r="B258" t="s">
+        <v>534</v>
+      </c>
+      <c r="C258" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
+        <v>260</v>
+      </c>
+      <c r="B259" t="s">
+        <v>663</v>
+      </c>
+      <c r="C259" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" t="s">
+        <v>261</v>
+      </c>
+      <c r="B260" t="s">
+        <v>664</v>
+      </c>
+      <c r="C260" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" t="s">
+        <v>262</v>
+      </c>
+      <c r="B261" t="s">
+        <v>637</v>
+      </c>
+      <c r="C261" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" t="s">
+        <v>263</v>
+      </c>
+      <c r="B262" t="s">
+        <v>588</v>
+      </c>
+      <c r="C262" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" t="s">
+        <v>264</v>
+      </c>
+      <c r="B263" t="s">
+        <v>665</v>
+      </c>
+      <c r="C263" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" t="s">
+        <v>265</v>
+      </c>
+      <c r="B264" t="s">
+        <v>666</v>
+      </c>
+      <c r="C264" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" t="s">
+        <v>266</v>
+      </c>
+      <c r="B265" t="s">
+        <v>667</v>
+      </c>
+      <c r="C265" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" t="s">
+        <v>267</v>
+      </c>
+      <c r="B266" t="s">
+        <v>534</v>
+      </c>
+      <c r="C266" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" t="s">
+        <v>268</v>
+      </c>
+      <c r="B267" t="s">
+        <v>626</v>
+      </c>
+      <c r="C267" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" t="s">
+        <v>269</v>
+      </c>
+      <c r="B268" t="s">
+        <v>625</v>
+      </c>
+      <c r="C268" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" t="s">
+        <v>270</v>
+      </c>
+      <c r="B269" t="s">
+        <v>668</v>
+      </c>
+      <c r="C269" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" t="s">
+        <v>271</v>
+      </c>
+      <c r="B270" t="s">
+        <v>669</v>
+      </c>
+      <c r="C270" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" t="s">
+        <v>272</v>
+      </c>
+      <c r="B271" t="s">
+        <v>624</v>
+      </c>
+      <c r="C271" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" t="s">
+        <v>273</v>
+      </c>
+      <c r="B272" t="s">
+        <v>670</v>
+      </c>
+      <c r="C272" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" t="s">
+        <v>274</v>
+      </c>
+      <c r="B273" t="s">
+        <v>671</v>
+      </c>
+      <c r="C273" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" t="s">
+        <v>275</v>
+      </c>
+      <c r="B274" t="s">
+        <v>672</v>
+      </c>
+      <c r="C274" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" t="s">
+        <v>276</v>
+      </c>
+      <c r="B275" t="s">
+        <v>618</v>
+      </c>
+      <c r="C275" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" t="s">
+        <v>277</v>
+      </c>
+      <c r="B276" t="s">
+        <v>588</v>
+      </c>
+      <c r="C276" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" t="s">
+        <v>278</v>
+      </c>
+      <c r="B277" t="s">
+        <v>616</v>
+      </c>
+      <c r="C277" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" t="s">
+        <v>279</v>
+      </c>
+      <c r="B278" t="s">
+        <v>473</v>
+      </c>
+      <c r="C278" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>280</v>
+      </c>
+      <c r="B279" t="s">
+        <v>673</v>
+      </c>
+      <c r="C279" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" t="s">
+        <v>281</v>
+      </c>
+      <c r="B280" t="s">
+        <v>667</v>
+      </c>
+      <c r="C280" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
+        <v>282</v>
+      </c>
+      <c r="B281" t="s">
+        <v>674</v>
+      </c>
+      <c r="C281" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
+        <v>283</v>
+      </c>
+      <c r="B282" t="s">
+        <v>675</v>
+      </c>
+      <c r="C282" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
+        <v>284</v>
+      </c>
+      <c r="B283" t="s">
+        <v>614</v>
+      </c>
+      <c r="C283" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" t="s">
+        <v>285</v>
+      </c>
+      <c r="B284" t="s">
+        <v>676</v>
+      </c>
+      <c r="C284" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
+        <v>286</v>
+      </c>
+      <c r="B285" t="s">
+        <v>677</v>
+      </c>
+      <c r="C285" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" t="s">
+        <v>287</v>
+      </c>
+      <c r="B286" t="s">
+        <v>678</v>
+      </c>
+      <c r="C286" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" t="s">
+        <v>288</v>
+      </c>
+      <c r="B287" t="s">
+        <v>679</v>
+      </c>
+      <c r="C287" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
+        <v>289</v>
+      </c>
+      <c r="B288" t="s">
+        <v>680</v>
+      </c>
+      <c r="C288" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" t="s">
+        <v>290</v>
+      </c>
+      <c r="B289" t="s">
+        <v>442</v>
+      </c>
+      <c r="C289" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" t="s">
+        <v>291</v>
+      </c>
+      <c r="B290" t="s">
+        <v>681</v>
+      </c>
+      <c r="C290" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" t="s">
+        <v>292</v>
+      </c>
+      <c r="B291" t="s">
+        <v>682</v>
+      </c>
+      <c r="C291" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" t="s">
+        <v>293</v>
+      </c>
+      <c r="B292" t="s">
+        <v>606</v>
+      </c>
+      <c r="C292" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" t="s">
+        <v>294</v>
+      </c>
+      <c r="B293" t="s">
+        <v>683</v>
+      </c>
+      <c r="C293" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" t="s">
+        <v>295</v>
+      </c>
+      <c r="B294" t="s">
+        <v>684</v>
+      </c>
+      <c r="C294" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" t="s">
+        <v>296</v>
+      </c>
+      <c r="B295" t="s">
+        <v>610</v>
+      </c>
+      <c r="C295" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" t="s">
+        <v>297</v>
+      </c>
+      <c r="B296" t="s">
+        <v>608</v>
+      </c>
+      <c r="C296" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" t="s">
+        <v>298</v>
+      </c>
+      <c r="B297" t="s">
+        <v>685</v>
+      </c>
+      <c r="C297" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" t="s">
+        <v>299</v>
+      </c>
+      <c r="B298" t="s">
+        <v>686</v>
+      </c>
+      <c r="C298" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" t="s">
+        <v>300</v>
+      </c>
+      <c r="B299" t="s">
+        <v>687</v>
+      </c>
+      <c r="C299" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" t="s">
+        <v>301</v>
+      </c>
+      <c r="B300" t="s">
+        <v>688</v>
+      </c>
+      <c r="C300" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" t="s">
+        <v>302</v>
+      </c>
+      <c r="B301" t="s">
+        <v>606</v>
+      </c>
+      <c r="C301" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
+        <v>303</v>
+      </c>
+      <c r="B302" t="s">
+        <v>605</v>
+      </c>
+      <c r="C302" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>304</v>
+      </c>
+      <c r="B303" t="s">
+        <v>689</v>
+      </c>
+      <c r="C303" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>305</v>
+      </c>
+      <c r="B304" t="s">
+        <v>690</v>
+      </c>
+      <c r="C304" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>306</v>
+      </c>
+      <c r="B305" t="s">
+        <v>604</v>
+      </c>
+      <c r="C305" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>307</v>
+      </c>
+      <c r="B306" t="s">
+        <v>691</v>
+      </c>
+      <c r="C306" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
+        <v>308</v>
+      </c>
+      <c r="B307" t="s">
+        <v>692</v>
+      </c>
+      <c r="C307" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>309</v>
+      </c>
+      <c r="B308" t="s">
+        <v>693</v>
+      </c>
+      <c r="C308" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
+        <v>310</v>
+      </c>
+      <c r="B309" t="s">
+        <v>602</v>
+      </c>
+      <c r="C309" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" t="s">
+        <v>311</v>
+      </c>
+      <c r="B310" t="s">
+        <v>694</v>
+      </c>
+      <c r="C310" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" t="s">
+        <v>312</v>
+      </c>
+      <c r="B311" t="s">
+        <v>600</v>
+      </c>
+      <c r="C311" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" t="s">
+        <v>313</v>
+      </c>
+      <c r="B312" t="s">
+        <v>695</v>
+      </c>
+      <c r="C312" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" t="s">
+        <v>314</v>
+      </c>
+      <c r="B313" t="s">
+        <v>696</v>
+      </c>
+      <c r="C313" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" t="s">
+        <v>315</v>
+      </c>
+      <c r="B314" t="s">
+        <v>697</v>
+      </c>
+      <c r="C314" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" t="s">
+        <v>316</v>
+      </c>
+      <c r="B315" t="s">
+        <v>598</v>
+      </c>
+      <c r="C315" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" t="s">
+        <v>317</v>
+      </c>
+      <c r="B316" t="s">
+        <v>698</v>
+      </c>
+      <c r="C316" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" t="s">
+        <v>318</v>
+      </c>
+      <c r="B317" t="s">
+        <v>595</v>
+      </c>
+      <c r="C317" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" t="s">
+        <v>319</v>
+      </c>
+      <c r="B318" t="s">
+        <v>699</v>
+      </c>
+      <c r="C318" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" t="s">
+        <v>320</v>
+      </c>
+      <c r="B319" t="s">
+        <v>700</v>
+      </c>
+      <c r="C319" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" t="s">
+        <v>321</v>
+      </c>
+      <c r="C320" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" t="s">
+        <v>322</v>
+      </c>
+      <c r="B321" t="s">
+        <v>701</v>
+      </c>
+      <c r="C321" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" t="s">
+        <v>323</v>
+      </c>
+      <c r="B322" t="s">
+        <v>702</v>
+      </c>
+      <c r="C322" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" t="s">
+        <v>324</v>
+      </c>
+      <c r="B323" t="s">
+        <v>703</v>
+      </c>
+      <c r="C323" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" t="s">
+        <v>325</v>
+      </c>
+      <c r="B324" t="s">
+        <v>704</v>
+      </c>
+      <c r="C324" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" t="s">
+        <v>326</v>
+      </c>
+      <c r="B325" t="s">
+        <v>705</v>
+      </c>
+      <c r="C325" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>327</v>
+      </c>
+      <c r="B326" t="s">
+        <v>588</v>
+      </c>
+      <c r="C326" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>328</v>
+      </c>
+      <c r="B327" t="s">
+        <v>706</v>
+      </c>
+      <c r="C327" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>329</v>
+      </c>
+      <c r="B328" t="s">
+        <v>707</v>
+      </c>
+      <c r="C328" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>330</v>
+      </c>
+      <c r="B329" t="s">
+        <v>708</v>
+      </c>
+      <c r="C329" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
+        <v>331</v>
+      </c>
+      <c r="B330" t="s">
+        <v>709</v>
+      </c>
+      <c r="C330" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
+        <v>332</v>
+      </c>
+      <c r="B331" t="s">
+        <v>710</v>
+      </c>
+      <c r="C331" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" t="s">
+        <v>333</v>
+      </c>
+      <c r="B332" t="s">
+        <v>534</v>
+      </c>
+      <c r="C332" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" t="s">
+        <v>334</v>
+      </c>
+      <c r="B333" t="s">
+        <v>588</v>
+      </c>
+      <c r="C333" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" t="s">
+        <v>335</v>
+      </c>
+      <c r="B334" t="s">
+        <v>583</v>
+      </c>
+      <c r="C334" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" t="s">
+        <v>336</v>
+      </c>
+      <c r="B335" t="s">
+        <v>582</v>
+      </c>
+      <c r="C335" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" t="s">
+        <v>337</v>
+      </c>
+      <c r="B336" t="s">
+        <v>711</v>
+      </c>
+      <c r="C336" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" t="s">
+        <v>338</v>
+      </c>
+      <c r="B337" t="s">
+        <v>712</v>
+      </c>
+      <c r="C337" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" t="s">
+        <v>339</v>
+      </c>
+      <c r="B338" t="s">
+        <v>713</v>
+      </c>
+      <c r="C338" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" t="s">
+        <v>340</v>
+      </c>
+      <c r="B339" t="s">
+        <v>577</v>
+      </c>
+      <c r="C339" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" t="s">
+        <v>341</v>
+      </c>
+      <c r="B340" t="s">
+        <v>576</v>
+      </c>
+      <c r="C340" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" t="s">
+        <v>342</v>
+      </c>
+      <c r="B341" t="s">
+        <v>714</v>
+      </c>
+      <c r="C341" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" t="s">
+        <v>343</v>
+      </c>
+      <c r="C342" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" t="s">
+        <v>344</v>
+      </c>
+      <c r="B343" t="s">
+        <v>572</v>
+      </c>
+      <c r="C343" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" t="s">
+        <v>345</v>
+      </c>
+      <c r="B344" t="s">
+        <v>715</v>
+      </c>
+      <c r="C344" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" t="s">
+        <v>346</v>
+      </c>
+      <c r="B345" t="s">
+        <v>571</v>
+      </c>
+      <c r="C345" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" t="s">
+        <v>347</v>
+      </c>
+      <c r="B346" t="s">
+        <v>570</v>
+      </c>
+      <c r="C346" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" t="s">
+        <v>348</v>
+      </c>
+      <c r="B347" t="s">
+        <v>716</v>
+      </c>
+      <c r="C347" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" t="s">
+        <v>349</v>
+      </c>
+      <c r="B348" t="s">
+        <v>568</v>
+      </c>
+      <c r="C348" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" t="s">
+        <v>350</v>
+      </c>
+      <c r="B349" t="s">
+        <v>566</v>
+      </c>
+      <c r="C349" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" t="s">
+        <v>351</v>
+      </c>
+      <c r="B350" t="s">
+        <v>565</v>
+      </c>
+      <c r="C350" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" t="s">
+        <v>352</v>
+      </c>
+      <c r="B351" t="s">
+        <v>717</v>
+      </c>
+      <c r="C351" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" t="s">
+        <v>353</v>
+      </c>
+      <c r="B352" t="s">
+        <v>562</v>
+      </c>
+      <c r="C352" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" t="s">
+        <v>354</v>
+      </c>
+      <c r="B353" t="s">
+        <v>718</v>
+      </c>
+      <c r="C353" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" t="s">
+        <v>355</v>
+      </c>
+      <c r="B354" t="s">
+        <v>719</v>
+      </c>
+      <c r="C354" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" t="s">
+        <v>356</v>
+      </c>
+      <c r="B355" t="s">
+        <v>559</v>
+      </c>
+      <c r="C355" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" t="s">
+        <v>357</v>
+      </c>
+      <c r="B356" t="s">
+        <v>548</v>
+      </c>
+      <c r="C356" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" t="s">
+        <v>358</v>
+      </c>
+      <c r="B357" t="s">
+        <v>558</v>
+      </c>
+      <c r="C357" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" t="s">
+        <v>359</v>
+      </c>
+      <c r="B358" t="s">
+        <v>557</v>
+      </c>
+      <c r="C358" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" t="s">
+        <v>360</v>
+      </c>
+      <c r="B359" t="s">
+        <v>556</v>
+      </c>
+      <c r="C359" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" t="s">
+        <v>361</v>
+      </c>
+      <c r="B360" t="s">
+        <v>720</v>
+      </c>
+      <c r="C360" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" t="s">
+        <v>362</v>
+      </c>
+      <c r="B361" t="s">
+        <v>552</v>
+      </c>
+      <c r="C361" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" t="s">
+        <v>363</v>
+      </c>
+      <c r="B362" t="s">
+        <v>721</v>
+      </c>
+      <c r="C362" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" t="s">
+        <v>364</v>
+      </c>
+      <c r="B363" t="s">
+        <v>722</v>
+      </c>
+      <c r="C363" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" t="s">
+        <v>365</v>
+      </c>
+      <c r="B364" t="s">
+        <v>723</v>
+      </c>
+      <c r="C364" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" t="s">
+        <v>366</v>
+      </c>
+      <c r="B365" t="s">
+        <v>550</v>
+      </c>
+      <c r="C365" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" t="s">
+        <v>367</v>
+      </c>
+      <c r="B366" t="s">
+        <v>545</v>
+      </c>
+      <c r="C366" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" t="s">
+        <v>368</v>
+      </c>
+      <c r="B367" t="s">
+        <v>438</v>
+      </c>
+      <c r="C367" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" t="s">
+        <v>369</v>
+      </c>
+      <c r="B368" t="s">
+        <v>720</v>
+      </c>
+      <c r="C368" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" t="s">
+        <v>370</v>
+      </c>
+      <c r="B369" t="s">
+        <v>534</v>
+      </c>
+      <c r="C369" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" t="s">
+        <v>371</v>
+      </c>
+      <c r="B370" t="s">
+        <v>543</v>
+      </c>
+      <c r="C370" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" t="s">
+        <v>372</v>
+      </c>
+      <c r="B371" t="s">
+        <v>724</v>
+      </c>
+      <c r="C371" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" t="s">
+        <v>373</v>
+      </c>
+      <c r="B372" t="s">
+        <v>540</v>
+      </c>
+      <c r="C372" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" t="s">
+        <v>374</v>
+      </c>
+      <c r="B373" t="s">
+        <v>725</v>
+      </c>
+      <c r="C373" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" t="s">
+        <v>375</v>
+      </c>
+      <c r="B374" t="s">
+        <v>537</v>
+      </c>
+      <c r="C374" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" t="s">
+        <v>376</v>
+      </c>
+      <c r="B375" t="s">
+        <v>726</v>
+      </c>
+      <c r="C375" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" t="s">
+        <v>377</v>
+      </c>
+      <c r="B376" t="s">
+        <v>727</v>
+      </c>
+      <c r="C376" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" t="s">
+        <v>378</v>
+      </c>
+      <c r="B377" t="s">
+        <v>728</v>
+      </c>
+      <c r="C377" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" t="s">
+        <v>379</v>
+      </c>
+      <c r="B378" t="s">
+        <v>533</v>
+      </c>
+      <c r="C378" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" t="s">
+        <v>380</v>
+      </c>
+      <c r="B379" t="s">
+        <v>729</v>
+      </c>
+      <c r="C379" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" t="s">
+        <v>381</v>
+      </c>
+      <c r="B380" t="s">
+        <v>530</v>
+      </c>
+      <c r="C380" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" t="s">
+        <v>382</v>
+      </c>
+      <c r="B381" t="s">
+        <v>529</v>
+      </c>
+      <c r="C381" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" t="s">
+        <v>383</v>
+      </c>
+      <c r="B382" t="s">
+        <v>526</v>
+      </c>
+      <c r="C382" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" t="s">
+        <v>384</v>
+      </c>
+      <c r="B383" t="s">
+        <v>522</v>
+      </c>
+      <c r="C383" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" t="s">
+        <v>385</v>
+      </c>
+      <c r="B384" t="s">
+        <v>730</v>
+      </c>
+      <c r="C384" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" t="s">
+        <v>386</v>
+      </c>
+      <c r="B385" t="s">
+        <v>514</v>
+      </c>
+      <c r="C385" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" t="s">
+        <v>387</v>
+      </c>
+      <c r="B386" t="s">
+        <v>513</v>
+      </c>
+      <c r="C386" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" t="s">
+        <v>388</v>
+      </c>
+      <c r="B387" t="s">
+        <v>512</v>
+      </c>
+      <c r="C387" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" t="s">
+        <v>389</v>
+      </c>
+      <c r="B388" t="s">
+        <v>511</v>
+      </c>
+      <c r="C388" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
+        <v>390</v>
+      </c>
+      <c r="B389" t="s">
+        <v>509</v>
+      </c>
+      <c r="C389" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
+        <v>391</v>
+      </c>
+      <c r="B390" t="s">
+        <v>508</v>
+      </c>
+      <c r="C390" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" t="s">
+        <v>392</v>
+      </c>
+      <c r="B391" t="s">
+        <v>453</v>
+      </c>
+      <c r="C391" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
+        <v>393</v>
+      </c>
+      <c r="B392" t="s">
+        <v>506</v>
+      </c>
+      <c r="C392" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" t="s">
+        <v>394</v>
+      </c>
+      <c r="B393" t="s">
+        <v>731</v>
+      </c>
+      <c r="C393" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
+        <v>395</v>
+      </c>
+      <c r="B394" t="s">
+        <v>502</v>
+      </c>
+      <c r="C394" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
+        <v>396</v>
+      </c>
+      <c r="B395" t="s">
+        <v>500</v>
+      </c>
+      <c r="C395" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" t="s">
+        <v>397</v>
+      </c>
+      <c r="C396" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" t="s">
+        <v>398</v>
+      </c>
+      <c r="B397" t="s">
+        <v>497</v>
+      </c>
+      <c r="C397" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" t="s">
+        <v>399</v>
+      </c>
+      <c r="B398" t="s">
+        <v>444</v>
+      </c>
+      <c r="C398" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" t="s">
+        <v>400</v>
+      </c>
+      <c r="B399" t="s">
+        <v>732</v>
+      </c>
+      <c r="C399" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" t="s">
+        <v>401</v>
+      </c>
+      <c r="B400" t="s">
+        <v>492</v>
+      </c>
+      <c r="C400" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" t="s">
+        <v>402</v>
+      </c>
+      <c r="B401" t="s">
+        <v>489</v>
+      </c>
+      <c r="C401" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" t="s">
+        <v>403</v>
+      </c>
+      <c r="B402" t="s">
+        <v>486</v>
+      </c>
+      <c r="C402" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" t="s">
+        <v>404</v>
+      </c>
+      <c r="B403" t="s">
+        <v>733</v>
+      </c>
+      <c r="C403" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" t="s">
+        <v>405</v>
+      </c>
+      <c r="B404" t="s">
+        <v>484</v>
+      </c>
+      <c r="C404" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" t="s">
+        <v>406</v>
+      </c>
+      <c r="B405" t="s">
+        <v>483</v>
+      </c>
+      <c r="C405" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" t="s">
+        <v>407</v>
+      </c>
+      <c r="B406" t="s">
+        <v>482</v>
+      </c>
+      <c r="C406" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" t="s">
+        <v>408</v>
+      </c>
+      <c r="B407" t="s">
+        <v>565</v>
+      </c>
+      <c r="C407" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" t="s">
+        <v>409</v>
+      </c>
+      <c r="B408" t="s">
+        <v>480</v>
+      </c>
+      <c r="C408" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" t="s">
+        <v>410</v>
+      </c>
+      <c r="B409" t="s">
+        <v>443</v>
+      </c>
+      <c r="C409" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" t="s">
+        <v>411</v>
+      </c>
+      <c r="B410" t="s">
+        <v>479</v>
+      </c>
+      <c r="C410" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411" t="s">
+        <v>412</v>
+      </c>
+      <c r="B411" t="s">
+        <v>443</v>
+      </c>
+      <c r="C411" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" t="s">
+        <v>413</v>
+      </c>
+      <c r="B412" t="s">
+        <v>474</v>
+      </c>
+      <c r="C412" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" t="s">
+        <v>414</v>
+      </c>
+      <c r="B413" t="s">
+        <v>734</v>
+      </c>
+      <c r="C413" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" t="s">
+        <v>415</v>
+      </c>
+      <c r="B414" t="s">
+        <v>735</v>
+      </c>
+      <c r="C414" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" t="s">
+        <v>416</v>
+      </c>
+      <c r="B415" t="s">
+        <v>466</v>
+      </c>
+      <c r="C415" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" t="s">
+        <v>417</v>
+      </c>
+      <c r="B416" t="s">
+        <v>443</v>
+      </c>
+      <c r="C416" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" t="s">
+        <v>418</v>
+      </c>
+      <c r="B417" t="s">
+        <v>465</v>
+      </c>
+      <c r="C417" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" t="s">
+        <v>419</v>
+      </c>
+      <c r="B418" t="s">
+        <v>464</v>
+      </c>
+      <c r="C418" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" t="s">
+        <v>420</v>
+      </c>
+      <c r="B419" t="s">
+        <v>462</v>
+      </c>
+      <c r="C419" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" t="s">
+        <v>421</v>
+      </c>
+      <c r="B420" t="s">
+        <v>736</v>
+      </c>
+      <c r="C420" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" t="s">
+        <v>422</v>
+      </c>
+      <c r="B421" t="s">
+        <v>460</v>
+      </c>
+      <c r="C421" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" t="s">
+        <v>423</v>
+      </c>
+      <c r="B422" t="s">
+        <v>458</v>
+      </c>
+      <c r="C422" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423" t="s">
+        <v>424</v>
+      </c>
+      <c r="B423" t="s">
+        <v>457</v>
+      </c>
+      <c r="C423" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424" t="s">
+        <v>425</v>
+      </c>
+      <c r="B424" t="s">
+        <v>443</v>
+      </c>
+      <c r="C424" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425" t="s">
+        <v>426</v>
+      </c>
+      <c r="B425" t="s">
+        <v>454</v>
+      </c>
+      <c r="C425" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426" t="s">
+        <v>427</v>
+      </c>
+      <c r="B426" t="s">
+        <v>452</v>
+      </c>
+      <c r="C426" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" t="s">
+        <v>428</v>
+      </c>
+      <c r="B427" t="s">
+        <v>444</v>
+      </c>
+      <c r="C427" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428" t="s">
+        <v>429</v>
+      </c>
+      <c r="B428" t="s">
+        <v>442</v>
+      </c>
+      <c r="C428" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429" t="s">
+        <v>430</v>
+      </c>
+      <c r="B429" t="s">
+        <v>441</v>
+      </c>
+      <c r="C429" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430" t="s">
+        <v>431</v>
+      </c>
+      <c r="B430" t="s">
+        <v>439</v>
+      </c>
+      <c r="C430" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431" t="s">
+        <v>432</v>
+      </c>
+      <c r="B431" t="s">
+        <v>436</v>
+      </c>
+      <c r="C431" t="s">
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/miniGAM/Dados/lançamentos_não_encontrados_no_excel.xlsx
+++ b/miniGAM/Dados/lançamentos_não_encontrados_no_excel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="482">
   <si>
     <t>Título (Normalizado)</t>
   </si>
@@ -31,7 +31,1432 @@
     <t>143</t>
   </si>
   <si>
-    <t>0,00</t>
+    <t>18970071</t>
+  </si>
+  <si>
+    <t>L7002</t>
+  </si>
+  <si>
+    <t>1356</t>
+  </si>
+  <si>
+    <t>1359</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>1317</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>3189</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>951</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>965</t>
+  </si>
+  <si>
+    <t>1464</t>
+  </si>
+  <si>
+    <t>679</t>
+  </si>
+  <si>
+    <t>1408</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>2082</t>
+  </si>
+  <si>
+    <t>1313</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>3069</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>3724</t>
+  </si>
+  <si>
+    <t>1321</t>
+  </si>
+  <si>
+    <t>988</t>
+  </si>
+  <si>
+    <t>1299</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>1316</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>3725</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
+    <t>936</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>1250</t>
+  </si>
+  <si>
+    <t>48770071</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>1451</t>
+  </si>
+  <si>
+    <t>1139</t>
+  </si>
+  <si>
+    <t>1523</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>922</t>
+  </si>
+  <si>
+    <t>2336</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>1407</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>1304</t>
+  </si>
+  <si>
+    <t>2233</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>1264</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>1311</t>
+  </si>
+  <si>
+    <t>653</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>2081</t>
+  </si>
+  <si>
+    <t>946</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>1298</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>3225</t>
+  </si>
+  <si>
+    <t>1428</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>1411</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>1483</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>2176</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>2079</t>
+  </si>
+  <si>
+    <t>1531</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>3289</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>945</t>
+  </si>
+  <si>
+    <t>1329</t>
+  </si>
+  <si>
+    <t>78770071</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>924</t>
+  </si>
+  <si>
+    <t>1305</t>
+  </si>
+  <si>
+    <t>2175</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>814</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1301</t>
+  </si>
+  <si>
+    <t>722</t>
+  </si>
+  <si>
+    <t>1522</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>917</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>1227</t>
+  </si>
+  <si>
+    <t>95770071</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
+    <t>1881</t>
+  </si>
+  <si>
+    <t>1412</t>
+  </si>
+  <si>
+    <t>1138</t>
+  </si>
+  <si>
+    <t>1488</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>1882</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>1829</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1246</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>1413</t>
+  </si>
+  <si>
+    <t>1396</t>
+  </si>
+  <si>
+    <t>758</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>1414</t>
+  </si>
+  <si>
+    <t>678</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>2055</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>85770071</t>
+  </si>
+  <si>
+    <t>1880</t>
+  </si>
+  <si>
+    <t>767</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>1418</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>1406</t>
+  </si>
+  <si>
+    <t>1682</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>3385</t>
+  </si>
+  <si>
+    <t>941</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>1687</t>
+  </si>
+  <si>
+    <t>1395</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>674</t>
+  </si>
+  <si>
+    <t>1819</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>1849</t>
+  </si>
+  <si>
+    <t>2078</t>
+  </si>
+  <si>
+    <t>1884</t>
+  </si>
+  <si>
+    <t>1735</t>
+  </si>
+  <si>
+    <t>2355</t>
+  </si>
+  <si>
+    <t>1923</t>
+  </si>
+  <si>
+    <t>2645</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>2232</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>1826</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>1355</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1828</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>2647</t>
+  </si>
+  <si>
+    <t>1330</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>2080</t>
+  </si>
+  <si>
+    <t>1754</t>
+  </si>
+  <si>
+    <t>1324</t>
+  </si>
+  <si>
+    <t>1827</t>
+  </si>
+  <si>
+    <t>2357</t>
+  </si>
+  <si>
+    <t>3275</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>1405</t>
+  </si>
+  <si>
+    <t>2077</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>3550</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
+    <t>2570</t>
+  </si>
+  <si>
+    <t>3387</t>
+  </si>
+  <si>
+    <t>1309</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>1733</t>
+  </si>
+  <si>
+    <t>1393</t>
+  </si>
+  <si>
+    <t>3184</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>48322</t>
+  </si>
+  <si>
+    <t>1303</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>958</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>5090</t>
+  </si>
+  <si>
+    <t>48341</t>
+  </si>
+  <si>
+    <t>5514</t>
+  </si>
+  <si>
+    <t>2,07</t>
+  </si>
+  <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>4,37</t>
+  </si>
+  <si>
+    <t>6,15</t>
+  </si>
+  <si>
+    <t>6,19</t>
+  </si>
+  <si>
+    <t>6,35</t>
+  </si>
+  <si>
+    <t>7,84</t>
+  </si>
+  <si>
+    <t>8,04</t>
+  </si>
+  <si>
+    <t>836,83</t>
+  </si>
+  <si>
+    <t>8,58</t>
+  </si>
+  <si>
+    <t>9,37</t>
+  </si>
+  <si>
+    <t>10,24</t>
+  </si>
+  <si>
+    <t>11,04</t>
+  </si>
+  <si>
+    <t>11,35</t>
+  </si>
+  <si>
+    <t>12,45</t>
+  </si>
+  <si>
+    <t>13,24</t>
+  </si>
+  <si>
+    <t>13,68</t>
+  </si>
+  <si>
+    <t>14,28</t>
+  </si>
+  <si>
+    <t>16,82</t>
+  </si>
+  <si>
+    <t>16,96</t>
+  </si>
+  <si>
+    <t>282,27</t>
+  </si>
+  <si>
+    <t>19,77</t>
+  </si>
+  <si>
+    <t>20,44</t>
+  </si>
+  <si>
+    <t>22,25</t>
+  </si>
+  <si>
+    <t>24,76</t>
+  </si>
+  <si>
+    <t>24,84</t>
+  </si>
+  <si>
+    <t>26,47</t>
+  </si>
+  <si>
+    <t>26,98</t>
+  </si>
+  <si>
+    <t>35,70</t>
+  </si>
+  <si>
+    <t>103,92</t>
+  </si>
+  <si>
+    <t>36,66</t>
+  </si>
+  <si>
+    <t>38,50</t>
+  </si>
+  <si>
+    <t>408,44</t>
+  </si>
+  <si>
+    <t>38,80</t>
+  </si>
+  <si>
+    <t>39,00</t>
+  </si>
+  <si>
+    <t>39,33</t>
+  </si>
+  <si>
+    <t>39,71</t>
+  </si>
+  <si>
+    <t>41,04</t>
+  </si>
+  <si>
+    <t>42,31</t>
+  </si>
+  <si>
+    <t>43,24</t>
+  </si>
+  <si>
+    <t>43,66</t>
+  </si>
+  <si>
+    <t>508,50</t>
+  </si>
+  <si>
+    <t>48,75</t>
+  </si>
+  <si>
+    <t>48,90</t>
+  </si>
+  <si>
+    <t>51,23</t>
+  </si>
+  <si>
+    <t>51,71</t>
+  </si>
+  <si>
+    <t>263,54</t>
+  </si>
+  <si>
+    <t>52,44</t>
+  </si>
+  <si>
+    <t>53,40</t>
+  </si>
+  <si>
+    <t>56,47</t>
+  </si>
+  <si>
+    <t>59,04</t>
+  </si>
+  <si>
+    <t>61,59</t>
+  </si>
+  <si>
+    <t>62,06</t>
+  </si>
+  <si>
+    <t>62,44</t>
+  </si>
+  <si>
+    <t>64,36</t>
+  </si>
+  <si>
+    <t>66,06</t>
+  </si>
+  <si>
+    <t>173,84</t>
+  </si>
+  <si>
+    <t>67,10</t>
+  </si>
+  <si>
+    <t>69,31</t>
+  </si>
+  <si>
+    <t>69,68</t>
+  </si>
+  <si>
+    <t>69,84</t>
+  </si>
+  <si>
+    <t>70,50</t>
+  </si>
+  <si>
+    <t>71,10</t>
+  </si>
+  <si>
+    <t>76,86</t>
+  </si>
+  <si>
+    <t>79,04</t>
+  </si>
+  <si>
+    <t>83,44</t>
+  </si>
+  <si>
+    <t>303,32</t>
+  </si>
+  <si>
+    <t>86,06</t>
+  </si>
+  <si>
+    <t>86,72</t>
+  </si>
+  <si>
+    <t>90,91</t>
+  </si>
+  <si>
+    <t>91,76</t>
+  </si>
+  <si>
+    <t>91,77</t>
+  </si>
+  <si>
+    <t>94,80</t>
+  </si>
+  <si>
+    <t>96,34</t>
+  </si>
+  <si>
+    <t>96,71</t>
+  </si>
+  <si>
+    <t>97,29</t>
+  </si>
+  <si>
+    <t>101,08</t>
+  </si>
+  <si>
+    <t>101,88</t>
+  </si>
+  <si>
+    <t>102,92</t>
+  </si>
+  <si>
+    <t>103,31</t>
+  </si>
+  <si>
+    <t>103,61</t>
+  </si>
+  <si>
+    <t>107,68</t>
+  </si>
+  <si>
+    <t>108,68</t>
+  </si>
+  <si>
+    <t>110,64</t>
+  </si>
+  <si>
+    <t>113,08</t>
+  </si>
+  <si>
+    <t>115,08</t>
+  </si>
+  <si>
+    <t>115,46</t>
+  </si>
+  <si>
+    <t>116,22</t>
+  </si>
+  <si>
+    <t>117,36</t>
+  </si>
+  <si>
+    <t>567,73</t>
+  </si>
+  <si>
+    <t>119,16</t>
+  </si>
+  <si>
+    <t>119,77</t>
+  </si>
+  <si>
+    <t>129,12</t>
+  </si>
+  <si>
+    <t>130,44</t>
+  </si>
+  <si>
+    <t>133,22</t>
+  </si>
+  <si>
+    <t>135,00</t>
+  </si>
+  <si>
+    <t>135,79</t>
+  </si>
+  <si>
+    <t>137,01</t>
+  </si>
+  <si>
+    <t>137,84</t>
+  </si>
+  <si>
+    <t>140,52</t>
+  </si>
+  <si>
+    <t>140,45</t>
+  </si>
+  <si>
+    <t>142,16</t>
+  </si>
+  <si>
+    <t>142,38</t>
+  </si>
+  <si>
+    <t>146,17</t>
+  </si>
+  <si>
+    <t>146,65</t>
+  </si>
+  <si>
+    <t>155,77</t>
+  </si>
+  <si>
+    <t>1.153,48</t>
+  </si>
+  <si>
+    <t>166,72</t>
+  </si>
+  <si>
+    <t>167,75</t>
+  </si>
+  <si>
+    <t>176,98</t>
+  </si>
+  <si>
+    <t>180,40</t>
+  </si>
+  <si>
+    <t>183,65</t>
+  </si>
+  <si>
+    <t>185,76</t>
+  </si>
+  <si>
+    <t>204,73</t>
+  </si>
+  <si>
+    <t>206,31</t>
+  </si>
+  <si>
+    <t>206,59</t>
+  </si>
+  <si>
+    <t>209,25</t>
+  </si>
+  <si>
+    <t>211,80</t>
+  </si>
+  <si>
+    <t>215,82</t>
+  </si>
+  <si>
+    <t>217,80</t>
+  </si>
+  <si>
+    <t>221,40</t>
+  </si>
+  <si>
+    <t>227,31</t>
+  </si>
+  <si>
+    <t>946,01</t>
+  </si>
+  <si>
+    <t>235,33</t>
+  </si>
+  <si>
+    <t>238,53</t>
+  </si>
+  <si>
+    <t>239,20</t>
+  </si>
+  <si>
+    <t>239,49</t>
+  </si>
+  <si>
+    <t>242,73</t>
+  </si>
+  <si>
+    <t>242,98</t>
+  </si>
+  <si>
+    <t>245,95</t>
+  </si>
+  <si>
+    <t>245,78</t>
+  </si>
+  <si>
+    <t>248,09</t>
+  </si>
+  <si>
+    <t>248,37</t>
+  </si>
+  <si>
+    <t>250,48</t>
+  </si>
+  <si>
+    <t>250,26</t>
+  </si>
+  <si>
+    <t>254,98</t>
+  </si>
+  <si>
+    <t>256,08</t>
+  </si>
+  <si>
+    <t>385,27</t>
+  </si>
+  <si>
+    <t>265,07</t>
+  </si>
+  <si>
+    <t>266,19</t>
+  </si>
+  <si>
+    <t>265,96</t>
+  </si>
+  <si>
+    <t>266,93</t>
+  </si>
+  <si>
+    <t>271,39</t>
+  </si>
+  <si>
+    <t>272,44</t>
+  </si>
+  <si>
+    <t>277,61</t>
+  </si>
+  <si>
+    <t>284,49</t>
+  </si>
+  <si>
+    <t>291,20</t>
+  </si>
+  <si>
+    <t>292,67</t>
+  </si>
+  <si>
+    <t>294,52</t>
+  </si>
+  <si>
+    <t>299,99</t>
+  </si>
+  <si>
+    <t>310,24</t>
+  </si>
+  <si>
+    <t>339,54</t>
+  </si>
+  <si>
+    <t>314,26</t>
+  </si>
+  <si>
+    <t>316,11</t>
+  </si>
+  <si>
+    <t>318,14</t>
+  </si>
+  <si>
+    <t>323,61</t>
+  </si>
+  <si>
+    <t>324,56</t>
+  </si>
+  <si>
+    <t>327,85</t>
+  </si>
+  <si>
+    <t>331,07</t>
+  </si>
+  <si>
+    <t>332,02</t>
+  </si>
+  <si>
+    <t>333,89</t>
+  </si>
+  <si>
+    <t>332,36</t>
+  </si>
+  <si>
+    <t>343,11</t>
+  </si>
+  <si>
+    <t>345,34</t>
+  </si>
+  <si>
+    <t>345,90</t>
+  </si>
+  <si>
+    <t>352,23</t>
+  </si>
+  <si>
+    <t>353,84</t>
+  </si>
+  <si>
+    <t>354,28</t>
+  </si>
+  <si>
+    <t>1.382,04</t>
+  </si>
+  <si>
+    <t>363,60</t>
+  </si>
+  <si>
+    <t>362,31</t>
+  </si>
+  <si>
+    <t>364,73</t>
+  </si>
+  <si>
+    <t>380,12</t>
+  </si>
+  <si>
+    <t>391,33</t>
+  </si>
+  <si>
+    <t>800,96</t>
+  </si>
+  <si>
+    <t>402,43</t>
+  </si>
+  <si>
+    <t>403,18</t>
+  </si>
+  <si>
+    <t>407,14</t>
+  </si>
+  <si>
+    <t>411,72</t>
+  </si>
+  <si>
+    <t>413,34</t>
+  </si>
+  <si>
+    <t>415,47</t>
+  </si>
+  <si>
+    <t>418,78</t>
+  </si>
+  <si>
+    <t>420,45</t>
+  </si>
+  <si>
+    <t>420,83</t>
+  </si>
+  <si>
+    <t>421,62</t>
+  </si>
+  <si>
+    <t>423,23</t>
+  </si>
+  <si>
+    <t>423,39</t>
+  </si>
+  <si>
+    <t>425,23</t>
+  </si>
+  <si>
+    <t>427,75</t>
+  </si>
+  <si>
+    <t>435,92</t>
+  </si>
+  <si>
+    <t>438,04</t>
+  </si>
+  <si>
+    <t>437,71</t>
+  </si>
+  <si>
+    <t>473,71</t>
+  </si>
+  <si>
+    <t>480,65</t>
+  </si>
+  <si>
+    <t>486,08</t>
+  </si>
+  <si>
+    <t>495,47</t>
+  </si>
+  <si>
+    <t>496,56</t>
+  </si>
+  <si>
+    <t>497,84</t>
+  </si>
+  <si>
+    <t>501,92</t>
+  </si>
+  <si>
+    <t>511,91</t>
+  </si>
+  <si>
+    <t>519,95</t>
+  </si>
+  <si>
+    <t>528,51</t>
+  </si>
+  <si>
+    <t>534,26</t>
+  </si>
+  <si>
+    <t>537,13</t>
+  </si>
+  <si>
+    <t>538,87</t>
+  </si>
+  <si>
+    <t>550,40</t>
+  </si>
+  <si>
+    <t>570,60</t>
+  </si>
+  <si>
+    <t>571,68</t>
+  </si>
+  <si>
+    <t>588,43</t>
+  </si>
+  <si>
+    <t>589,92</t>
+  </si>
+  <si>
+    <t>608,75</t>
+  </si>
+  <si>
+    <t>625,72</t>
+  </si>
+  <si>
+    <t>636,86</t>
+  </si>
+  <si>
+    <t>654,73</t>
+  </si>
+  <si>
+    <t>666,99</t>
+  </si>
+  <si>
+    <t>669,25</t>
+  </si>
+  <si>
+    <t>676,04</t>
+  </si>
+  <si>
+    <t>686,91</t>
+  </si>
+  <si>
+    <t>693,14</t>
+  </si>
+  <si>
+    <t>696,97</t>
+  </si>
+  <si>
+    <t>709,85</t>
+  </si>
+  <si>
+    <t>725,49</t>
+  </si>
+  <si>
+    <t>735,18</t>
+  </si>
+  <si>
+    <t>753,12</t>
+  </si>
+  <si>
+    <t>759,38</t>
+  </si>
+  <si>
+    <t>783,44</t>
+  </si>
+  <si>
+    <t>801,53</t>
+  </si>
+  <si>
+    <t>809,12</t>
+  </si>
+  <si>
+    <t>814,57</t>
+  </si>
+  <si>
+    <t>929,56</t>
+  </si>
+  <si>
+    <t>1.037,59</t>
+  </si>
+  <si>
+    <t>1.095,56</t>
+  </si>
+  <si>
+    <t>1.190,24</t>
+  </si>
+  <si>
+    <t>1.995,70</t>
+  </si>
+  <si>
+    <t>2.589,83</t>
+  </si>
+  <si>
+    <t>5.671,20</t>
+  </si>
+  <si>
+    <t>5.871,04</t>
   </si>
   <si>
     <t>Lançamento visível no Consinco mas NÃO consta na planilha do Excel</t>
@@ -366,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -385,10 +1810,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -396,10 +1821,2639 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>263</v>
+      </c>
+      <c r="C23" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C25" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C26" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>268</v>
+      </c>
+      <c r="C28" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>270</v>
+      </c>
+      <c r="C30" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>270</v>
+      </c>
+      <c r="C31" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>272</v>
+      </c>
+      <c r="C33" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>276</v>
+      </c>
+      <c r="C37" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>279</v>
+      </c>
+      <c r="C40" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>284</v>
+      </c>
+      <c r="C45" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
+        <v>287</v>
+      </c>
+      <c r="C48" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>288</v>
+      </c>
+      <c r="C49" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>289</v>
+      </c>
+      <c r="C50" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>290</v>
+      </c>
+      <c r="C51" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
+        <v>291</v>
+      </c>
+      <c r="C52" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" t="s">
+        <v>292</v>
+      </c>
+      <c r="C53" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>293</v>
+      </c>
+      <c r="C54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" t="s">
+        <v>294</v>
+      </c>
+      <c r="C55" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>295</v>
+      </c>
+      <c r="C56" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>296</v>
+      </c>
+      <c r="C57" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>297</v>
+      </c>
+      <c r="C58" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>298</v>
+      </c>
+      <c r="C59" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" t="s">
+        <v>299</v>
+      </c>
+      <c r="C60" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>300</v>
+      </c>
+      <c r="C61" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>301</v>
+      </c>
+      <c r="C62" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>303</v>
+      </c>
+      <c r="C64" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C65" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" t="s">
+        <v>305</v>
+      </c>
+      <c r="C66" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" t="s">
+        <v>306</v>
+      </c>
+      <c r="C67" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" t="s">
+        <v>308</v>
+      </c>
+      <c r="C69" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" t="s">
+        <v>309</v>
+      </c>
+      <c r="C70" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" t="s">
+        <v>310</v>
+      </c>
+      <c r="C71" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" t="s">
+        <v>311</v>
+      </c>
+      <c r="C72" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" t="s">
+        <v>312</v>
+      </c>
+      <c r="C73" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" t="s">
+        <v>313</v>
+      </c>
+      <c r="C74" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" t="s">
+        <v>314</v>
+      </c>
+      <c r="C75" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
+        <v>315</v>
+      </c>
+      <c r="C76" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" t="s">
+        <v>316</v>
+      </c>
+      <c r="C77" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" t="s">
+        <v>317</v>
+      </c>
+      <c r="C78" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" t="s">
+        <v>318</v>
+      </c>
+      <c r="C79" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" t="s">
+        <v>319</v>
+      </c>
+      <c r="C80" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>320</v>
+      </c>
+      <c r="C81" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" t="s">
+        <v>321</v>
+      </c>
+      <c r="C82" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" t="s">
+        <v>323</v>
+      </c>
+      <c r="C84" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C85" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" t="s">
+        <v>325</v>
+      </c>
+      <c r="C86" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" t="s">
+        <v>326</v>
+      </c>
+      <c r="C87" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="s">
+        <v>326</v>
+      </c>
+      <c r="C88" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" t="s">
+        <v>327</v>
+      </c>
+      <c r="C89" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" t="s">
+        <v>328</v>
+      </c>
+      <c r="C90" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" t="s">
+        <v>329</v>
+      </c>
+      <c r="C91" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" t="s">
+        <v>330</v>
+      </c>
+      <c r="C92" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" t="s">
+        <v>331</v>
+      </c>
+      <c r="C93" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" t="s">
+        <v>332</v>
+      </c>
+      <c r="C94" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" t="s">
+        <v>333</v>
+      </c>
+      <c r="C95" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" t="s">
+        <v>334</v>
+      </c>
+      <c r="C96" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>335</v>
+      </c>
+      <c r="C97" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" t="s">
+        <v>336</v>
+      </c>
+      <c r="C98" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" t="s">
+        <v>337</v>
+      </c>
+      <c r="C99" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" t="s">
+        <v>338</v>
+      </c>
+      <c r="C100" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="s">
+        <v>339</v>
+      </c>
+      <c r="C101" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" t="s">
+        <v>340</v>
+      </c>
+      <c r="C102" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" t="s">
+        <v>341</v>
+      </c>
+      <c r="C103" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
+        <v>342</v>
+      </c>
+      <c r="C104" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" t="s">
+        <v>343</v>
+      </c>
+      <c r="C105" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
+        <v>344</v>
+      </c>
+      <c r="C106" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" t="s">
+        <v>345</v>
+      </c>
+      <c r="C107" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" t="s">
+        <v>346</v>
+      </c>
+      <c r="C108" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" t="s">
+        <v>347</v>
+      </c>
+      <c r="C109" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" t="s">
+        <v>348</v>
+      </c>
+      <c r="C110" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" t="s">
+        <v>349</v>
+      </c>
+      <c r="C111" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" t="s">
+        <v>350</v>
+      </c>
+      <c r="C112" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" t="s">
+        <v>351</v>
+      </c>
+      <c r="C113" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" t="s">
+        <v>352</v>
+      </c>
+      <c r="C114" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" t="s">
+        <v>353</v>
+      </c>
+      <c r="C115" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" t="s">
+        <v>354</v>
+      </c>
+      <c r="C116" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" t="s">
+        <v>356</v>
+      </c>
+      <c r="C118" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" t="s">
+        <v>357</v>
+      </c>
+      <c r="C119" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" t="s">
+        <v>358</v>
+      </c>
+      <c r="C120" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" t="s">
+        <v>359</v>
+      </c>
+      <c r="C121" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" t="s">
+        <v>360</v>
+      </c>
+      <c r="C122" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" t="s">
+        <v>361</v>
+      </c>
+      <c r="C123" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" t="s">
+        <v>362</v>
+      </c>
+      <c r="C124" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" t="s">
+        <v>363</v>
+      </c>
+      <c r="C125" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" t="s">
+        <v>364</v>
+      </c>
+      <c r="C126" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" t="s">
+        <v>365</v>
+      </c>
+      <c r="C127" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" t="s">
+        <v>366</v>
+      </c>
+      <c r="C128" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" t="s">
+        <v>367</v>
+      </c>
+      <c r="C129" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" t="s">
+        <v>368</v>
+      </c>
+      <c r="C130" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" t="s">
+        <v>369</v>
+      </c>
+      <c r="C131" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B132" t="s">
+        <v>370</v>
+      </c>
+      <c r="C132" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>134</v>
+      </c>
+      <c r="B133" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>135</v>
+      </c>
+      <c r="B134" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="s">
+        <v>373</v>
+      </c>
+      <c r="C135" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" t="s">
+        <v>374</v>
+      </c>
+      <c r="C136" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137" t="s">
+        <v>375</v>
+      </c>
+      <c r="C137" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" t="s">
+        <v>376</v>
+      </c>
+      <c r="C138" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>140</v>
+      </c>
+      <c r="B139" t="s">
+        <v>377</v>
+      </c>
+      <c r="C139" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" t="s">
+        <v>378</v>
+      </c>
+      <c r="C140" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="s">
+        <v>379</v>
+      </c>
+      <c r="C141" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" t="s">
+        <v>380</v>
+      </c>
+      <c r="C142" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" t="s">
+        <v>381</v>
+      </c>
+      <c r="C143" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144" t="s">
+        <v>382</v>
+      </c>
+      <c r="C144" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" t="s">
+        <v>383</v>
+      </c>
+      <c r="C145" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" t="s">
+        <v>384</v>
+      </c>
+      <c r="C146" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>148</v>
+      </c>
+      <c r="B147" t="s">
+        <v>385</v>
+      </c>
+      <c r="C147" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" t="s">
+        <v>386</v>
+      </c>
+      <c r="C148" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" t="s">
+        <v>387</v>
+      </c>
+      <c r="C149" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" t="s">
+        <v>388</v>
+      </c>
+      <c r="C150" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" t="s">
+        <v>389</v>
+      </c>
+      <c r="C151" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152" t="s">
+        <v>390</v>
+      </c>
+      <c r="C152" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" t="s">
+        <v>391</v>
+      </c>
+      <c r="C153" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" t="s">
+        <v>392</v>
+      </c>
+      <c r="C154" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" t="s">
+        <v>393</v>
+      </c>
+      <c r="C155" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>158</v>
+      </c>
+      <c r="B157" t="s">
+        <v>395</v>
+      </c>
+      <c r="C157" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>159</v>
+      </c>
+      <c r="B158" t="s">
+        <v>396</v>
+      </c>
+      <c r="C158" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>160</v>
+      </c>
+      <c r="B159" t="s">
+        <v>397</v>
+      </c>
+      <c r="C159" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>161</v>
+      </c>
+      <c r="B160" t="s">
+        <v>398</v>
+      </c>
+      <c r="C160" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>162</v>
+      </c>
+      <c r="B161" t="s">
+        <v>399</v>
+      </c>
+      <c r="C161" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162" t="s">
+        <v>400</v>
+      </c>
+      <c r="C162" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
+        <v>164</v>
+      </c>
+      <c r="B163" t="s">
+        <v>401</v>
+      </c>
+      <c r="C163" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
+        <v>165</v>
+      </c>
+      <c r="B164" t="s">
+        <v>402</v>
+      </c>
+      <c r="C164" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
+        <v>166</v>
+      </c>
+      <c r="B165" t="s">
+        <v>403</v>
+      </c>
+      <c r="C165" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>167</v>
+      </c>
+      <c r="B166" t="s">
+        <v>404</v>
+      </c>
+      <c r="C166" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
+        <v>168</v>
+      </c>
+      <c r="B167" t="s">
+        <v>405</v>
+      </c>
+      <c r="C167" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>169</v>
+      </c>
+      <c r="B168" t="s">
+        <v>406</v>
+      </c>
+      <c r="C168" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
+        <v>170</v>
+      </c>
+      <c r="B169" t="s">
+        <v>407</v>
+      </c>
+      <c r="C169" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
+        <v>171</v>
+      </c>
+      <c r="B170" t="s">
+        <v>408</v>
+      </c>
+      <c r="C170" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
+        <v>172</v>
+      </c>
+      <c r="B171" t="s">
+        <v>409</v>
+      </c>
+      <c r="C171" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172" t="s">
+        <v>410</v>
+      </c>
+      <c r="C172" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
+        <v>174</v>
+      </c>
+      <c r="B173" t="s">
+        <v>411</v>
+      </c>
+      <c r="C173" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174" t="s">
+        <v>412</v>
+      </c>
+      <c r="C174" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
+        <v>176</v>
+      </c>
+      <c r="B175" t="s">
+        <v>413</v>
+      </c>
+      <c r="C175" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
+        <v>177</v>
+      </c>
+      <c r="B176" t="s">
+        <v>414</v>
+      </c>
+      <c r="C176" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
+        <v>178</v>
+      </c>
+      <c r="B177" t="s">
+        <v>415</v>
+      </c>
+      <c r="C177" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
+        <v>179</v>
+      </c>
+      <c r="B178" t="s">
+        <v>416</v>
+      </c>
+      <c r="C178" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
+        <v>180</v>
+      </c>
+      <c r="B179" t="s">
+        <v>417</v>
+      </c>
+      <c r="C179" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" t="s">
+        <v>418</v>
+      </c>
+      <c r="C180" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181" t="s">
+        <v>419</v>
+      </c>
+      <c r="C181" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
+        <v>183</v>
+      </c>
+      <c r="B182" t="s">
+        <v>420</v>
+      </c>
+      <c r="C182" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183" t="s">
+        <v>421</v>
+      </c>
+      <c r="C183" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
+        <v>185</v>
+      </c>
+      <c r="B184" t="s">
+        <v>422</v>
+      </c>
+      <c r="C184" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
+        <v>186</v>
+      </c>
+      <c r="B185" t="s">
+        <v>423</v>
+      </c>
+      <c r="C185" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
+        <v>187</v>
+      </c>
+      <c r="B186" t="s">
+        <v>424</v>
+      </c>
+      <c r="C186" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
+        <v>188</v>
+      </c>
+      <c r="B187" t="s">
+        <v>425</v>
+      </c>
+      <c r="C187" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
+        <v>189</v>
+      </c>
+      <c r="B188" t="s">
+        <v>426</v>
+      </c>
+      <c r="C188" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
+        <v>190</v>
+      </c>
+      <c r="B189" t="s">
+        <v>427</v>
+      </c>
+      <c r="C189" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
+        <v>191</v>
+      </c>
+      <c r="B190" t="s">
+        <v>428</v>
+      </c>
+      <c r="C190" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
+        <v>192</v>
+      </c>
+      <c r="B191" t="s">
+        <v>429</v>
+      </c>
+      <c r="C191" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>193</v>
+      </c>
+      <c r="B192" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
+        <v>194</v>
+      </c>
+      <c r="B193" t="s">
+        <v>431</v>
+      </c>
+      <c r="C193" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
+        <v>195</v>
+      </c>
+      <c r="B194" t="s">
+        <v>432</v>
+      </c>
+      <c r="C194" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
+        <v>196</v>
+      </c>
+      <c r="B195" t="s">
+        <v>433</v>
+      </c>
+      <c r="C195" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
+        <v>197</v>
+      </c>
+      <c r="B196" t="s">
+        <v>434</v>
+      </c>
+      <c r="C196" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
+        <v>198</v>
+      </c>
+      <c r="B197" t="s">
+        <v>435</v>
+      </c>
+      <c r="C197" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
+        <v>199</v>
+      </c>
+      <c r="B198" t="s">
+        <v>436</v>
+      </c>
+      <c r="C198" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
+        <v>200</v>
+      </c>
+      <c r="B199" t="s">
+        <v>437</v>
+      </c>
+      <c r="C199" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
+        <v>201</v>
+      </c>
+      <c r="B200" t="s">
+        <v>438</v>
+      </c>
+      <c r="C200" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
+        <v>202</v>
+      </c>
+      <c r="B201" t="s">
+        <v>439</v>
+      </c>
+      <c r="C201" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
+        <v>203</v>
+      </c>
+      <c r="B202" t="s">
+        <v>440</v>
+      </c>
+      <c r="C202" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
+        <v>204</v>
+      </c>
+      <c r="B203" t="s">
+        <v>441</v>
+      </c>
+      <c r="C203" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
+        <v>205</v>
+      </c>
+      <c r="B204" t="s">
+        <v>442</v>
+      </c>
+      <c r="C204" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
+        <v>206</v>
+      </c>
+      <c r="B205" t="s">
+        <v>443</v>
+      </c>
+      <c r="C205" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
+        <v>207</v>
+      </c>
+      <c r="B206" t="s">
+        <v>444</v>
+      </c>
+      <c r="C206" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
+        <v>208</v>
+      </c>
+      <c r="B207" t="s">
+        <v>445</v>
+      </c>
+      <c r="C207" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
+        <v>209</v>
+      </c>
+      <c r="B208" t="s">
+        <v>446</v>
+      </c>
+      <c r="C208" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209" t="s">
+        <v>447</v>
+      </c>
+      <c r="C209" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" t="s">
+        <v>211</v>
+      </c>
+      <c r="B210" t="s">
+        <v>448</v>
+      </c>
+      <c r="C210" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" t="s">
+        <v>212</v>
+      </c>
+      <c r="B211" t="s">
+        <v>449</v>
+      </c>
+      <c r="C211" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" t="s">
+        <v>213</v>
+      </c>
+      <c r="B212" t="s">
+        <v>450</v>
+      </c>
+      <c r="C212" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" t="s">
+        <v>214</v>
+      </c>
+      <c r="B213" t="s">
+        <v>451</v>
+      </c>
+      <c r="C213" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" t="s">
+        <v>215</v>
+      </c>
+      <c r="B214" t="s">
+        <v>452</v>
+      </c>
+      <c r="C214" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215" t="s">
+        <v>453</v>
+      </c>
+      <c r="C215" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+      <c r="B216" t="s">
+        <v>454</v>
+      </c>
+      <c r="C216" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+      <c r="B217" t="s">
+        <v>455</v>
+      </c>
+      <c r="C217" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+      <c r="B218" t="s">
+        <v>456</v>
+      </c>
+      <c r="C218" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+      <c r="B219" t="s">
+        <v>457</v>
+      </c>
+      <c r="C219" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+      <c r="B220" t="s">
+        <v>458</v>
+      </c>
+      <c r="C220" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+      <c r="B221" t="s">
+        <v>459</v>
+      </c>
+      <c r="C221" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+      <c r="B222" t="s">
+        <v>460</v>
+      </c>
+      <c r="C222" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+      <c r="B223" t="s">
+        <v>461</v>
+      </c>
+      <c r="C223" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>225</v>
+      </c>
+      <c r="B224" t="s">
+        <v>462</v>
+      </c>
+      <c r="C224" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
+        <v>226</v>
+      </c>
+      <c r="B225" t="s">
+        <v>463</v>
+      </c>
+      <c r="C225" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
+        <v>227</v>
+      </c>
+      <c r="B226" t="s">
+        <v>464</v>
+      </c>
+      <c r="C226" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" t="s">
+        <v>228</v>
+      </c>
+      <c r="B227" t="s">
+        <v>465</v>
+      </c>
+      <c r="C227" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228" t="s">
+        <v>229</v>
+      </c>
+      <c r="B228" t="s">
+        <v>466</v>
+      </c>
+      <c r="C228" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
+        <v>230</v>
+      </c>
+      <c r="B229" t="s">
+        <v>467</v>
+      </c>
+      <c r="C229" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
+        <v>231</v>
+      </c>
+      <c r="B230" t="s">
+        <v>468</v>
+      </c>
+      <c r="C230" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" t="s">
+        <v>232</v>
+      </c>
+      <c r="B231" t="s">
+        <v>469</v>
+      </c>
+      <c r="C231" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>233</v>
+      </c>
+      <c r="B232" t="s">
+        <v>470</v>
+      </c>
+      <c r="C232" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" t="s">
+        <v>234</v>
+      </c>
+      <c r="B233" t="s">
+        <v>471</v>
+      </c>
+      <c r="C233" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" t="s">
+        <v>235</v>
+      </c>
+      <c r="B234" t="s">
+        <v>472</v>
+      </c>
+      <c r="C234" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
+        <v>236</v>
+      </c>
+      <c r="B235" t="s">
+        <v>473</v>
+      </c>
+      <c r="C235" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>237</v>
+      </c>
+      <c r="B236" t="s">
+        <v>474</v>
+      </c>
+      <c r="C236" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
+        <v>238</v>
+      </c>
+      <c r="B237" t="s">
+        <v>475</v>
+      </c>
+      <c r="C237" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238" t="s">
+        <v>476</v>
+      </c>
+      <c r="C238" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
+        <v>240</v>
+      </c>
+      <c r="B239" t="s">
+        <v>477</v>
+      </c>
+      <c r="C239" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
+        <v>241</v>
+      </c>
+      <c r="B240" t="s">
+        <v>478</v>
+      </c>
+      <c r="C240" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" t="s">
+        <v>242</v>
+      </c>
+      <c r="B241" t="s">
+        <v>479</v>
+      </c>
+      <c r="C241" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
+        <v>243</v>
+      </c>
+      <c r="B242" t="s">
+        <v>480</v>
+      </c>
+      <c r="C242" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>
